--- a/browser/assets/kpi-sheets/overall_kpi_2026_01.xlsx
+++ b/browser/assets/kpi-sheets/overall_kpi_2026_01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathu\OneDrive\Desktop\KPI\KPIMonitoring\KPIMonitoring\browser\assets\kpi-sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sltcomlk-my.sharepoint.com/personal/015897_intranet_slt_com_lk/Documents/Documents/NW Eng KPI Improvement/KPI 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F3B460-3ED0-42EE-96A9-27E13137A7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{FC60A20F-D631-4214-A61C-61DA62BD7EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{072447A6-B48D-4F31-A2E3-084B97DBE56B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4800" yWindow="1020" windowWidth="14400" windowHeight="7270" xr2:uid="{71964CE1-C6D4-4375-8411-FC98F6D5E7DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{71964CE1-C6D4-4375-8411-FC98F6D5E7DC}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI Calculation" sheetId="1" r:id="rId1"/>
@@ -26,13 +26,21 @@
   <externalReferences>
     <externalReference r:id="rId10"/>
   </externalReferences>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1049,7 +1057,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3106,10 +3114,58 @@
     <xf numFmtId="10" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3118,13 +3174,55 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3232,132 +3330,69 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3367,18 +3402,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3397,25 +3420,13 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3431,15 +3442,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3457,46 +3459,52 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="3" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3505,7 +3513,7 @@
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Baseline Operationa plan_v2 2" xfId="4" xr:uid="{55CE3B4E-2478-4D52-8202-6AA633AB7DDD}"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -3534,7 +3542,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4145,6 +4153,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4152,7 +4161,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4772,8 +4780,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="E_NW_NEW FORMAT"/>
       <sheetName val="E_NW"/>
@@ -5172,433 +5183,433 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624FE89F-9FAB-4C7C-845E-153E2232396E}">
   <dimension ref="A1:BP31"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="5" width="33.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="4" width="19.7109375" customWidth="1"/>
+    <col min="5" max="5" width="33.85546875" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="11.4140625" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="14.5" thickBot="1">
-      <c r="I1" s="287" t="s">
+    <row r="1" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="317" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="288"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
-      <c r="M1" s="289"/>
-      <c r="N1" s="289"/>
-      <c r="O1" s="289"/>
-      <c r="P1" s="289"/>
-      <c r="Q1" s="289"/>
-      <c r="R1" s="289"/>
-      <c r="S1" s="289"/>
-      <c r="T1" s="289"/>
-      <c r="U1" s="289"/>
-      <c r="V1" s="290"/>
-      <c r="W1" s="291"/>
-      <c r="X1" s="292" t="s">
+      <c r="J1" s="318"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
+      <c r="M1" s="319"/>
+      <c r="N1" s="319"/>
+      <c r="O1" s="319"/>
+      <c r="P1" s="319"/>
+      <c r="Q1" s="319"/>
+      <c r="R1" s="319"/>
+      <c r="S1" s="319"/>
+      <c r="T1" s="319"/>
+      <c r="U1" s="319"/>
+      <c r="V1" s="320"/>
+      <c r="W1" s="321"/>
+      <c r="X1" s="322" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="293"/>
-      <c r="Z1" s="293"/>
-      <c r="AA1" s="293"/>
-      <c r="AB1" s="293"/>
-      <c r="AC1" s="293"/>
-      <c r="AD1" s="293"/>
-      <c r="AE1" s="293"/>
-      <c r="AF1" s="293"/>
-      <c r="AG1" s="293"/>
-      <c r="AH1" s="293"/>
-      <c r="AI1" s="293"/>
-      <c r="AJ1" s="293"/>
-      <c r="AK1" s="293"/>
-      <c r="AL1" s="293"/>
-      <c r="AM1" s="293"/>
-      <c r="AN1" s="293"/>
-      <c r="AO1" s="294"/>
-      <c r="AP1" s="295" t="s">
+      <c r="Y1" s="323"/>
+      <c r="Z1" s="323"/>
+      <c r="AA1" s="323"/>
+      <c r="AB1" s="323"/>
+      <c r="AC1" s="323"/>
+      <c r="AD1" s="323"/>
+      <c r="AE1" s="323"/>
+      <c r="AF1" s="323"/>
+      <c r="AG1" s="323"/>
+      <c r="AH1" s="323"/>
+      <c r="AI1" s="323"/>
+      <c r="AJ1" s="323"/>
+      <c r="AK1" s="323"/>
+      <c r="AL1" s="323"/>
+      <c r="AM1" s="323"/>
+      <c r="AN1" s="323"/>
+      <c r="AO1" s="324"/>
+      <c r="AP1" s="325" t="s">
         <v>13</v>
       </c>
-      <c r="AQ1" s="296"/>
-      <c r="AR1" s="297"/>
-      <c r="AS1" s="297"/>
-      <c r="AT1" s="297"/>
-      <c r="AU1" s="297"/>
-      <c r="AV1" s="297"/>
-      <c r="AW1" s="297"/>
-      <c r="AX1" s="297"/>
-      <c r="AY1" s="297"/>
-      <c r="AZ1" s="297"/>
-      <c r="BA1" s="297"/>
-      <c r="BB1" s="297"/>
-      <c r="BC1" s="298"/>
-      <c r="BD1" s="299"/>
-      <c r="BE1" s="300" t="s">
+      <c r="AQ1" s="326"/>
+      <c r="AR1" s="327"/>
+      <c r="AS1" s="327"/>
+      <c r="AT1" s="327"/>
+      <c r="AU1" s="327"/>
+      <c r="AV1" s="327"/>
+      <c r="AW1" s="327"/>
+      <c r="AX1" s="327"/>
+      <c r="AY1" s="327"/>
+      <c r="AZ1" s="327"/>
+      <c r="BA1" s="327"/>
+      <c r="BB1" s="327"/>
+      <c r="BC1" s="328"/>
+      <c r="BD1" s="329"/>
+      <c r="BE1" s="330" t="s">
         <v>14</v>
       </c>
-      <c r="BF1" s="301"/>
-      <c r="BG1" s="301"/>
-      <c r="BH1" s="301"/>
-      <c r="BI1" s="301"/>
-      <c r="BJ1" s="301"/>
-      <c r="BK1" s="301"/>
-      <c r="BL1" s="301"/>
-      <c r="BM1" s="301"/>
-      <c r="BN1" s="301"/>
-      <c r="BO1" s="301"/>
-      <c r="BP1" s="302"/>
-    </row>
-    <row r="2" spans="1:68" ht="14.5" thickBot="1">
-      <c r="I2" s="303" t="s">
+      <c r="BF1" s="331"/>
+      <c r="BG1" s="331"/>
+      <c r="BH1" s="331"/>
+      <c r="BI1" s="331"/>
+      <c r="BJ1" s="331"/>
+      <c r="BK1" s="331"/>
+      <c r="BL1" s="331"/>
+      <c r="BM1" s="331"/>
+      <c r="BN1" s="331"/>
+      <c r="BO1" s="331"/>
+      <c r="BP1" s="332"/>
+    </row>
+    <row r="2" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="333" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="304"/>
-      <c r="K2" s="305"/>
-      <c r="L2" s="305"/>
-      <c r="M2" s="305"/>
-      <c r="N2" s="305"/>
-      <c r="O2" s="305"/>
-      <c r="P2" s="306"/>
-      <c r="Q2" s="306"/>
-      <c r="R2" s="307" t="s">
+      <c r="J2" s="334"/>
+      <c r="K2" s="335"/>
+      <c r="L2" s="335"/>
+      <c r="M2" s="335"/>
+      <c r="N2" s="335"/>
+      <c r="O2" s="335"/>
+      <c r="P2" s="336"/>
+      <c r="Q2" s="336"/>
+      <c r="R2" s="337" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="308"/>
-      <c r="T2" s="309"/>
-      <c r="U2" s="309"/>
-      <c r="V2" s="310"/>
-      <c r="W2" s="311"/>
-      <c r="X2" s="312" t="s">
+      <c r="S2" s="338"/>
+      <c r="T2" s="339"/>
+      <c r="U2" s="339"/>
+      <c r="V2" s="340"/>
+      <c r="W2" s="341"/>
+      <c r="X2" s="342" t="s">
         <v>17</v>
       </c>
-      <c r="Y2" s="313"/>
-      <c r="Z2" s="313"/>
-      <c r="AA2" s="313"/>
-      <c r="AB2" s="313"/>
-      <c r="AC2" s="314"/>
-      <c r="AD2" s="315" t="s">
+      <c r="Y2" s="343"/>
+      <c r="Z2" s="343"/>
+      <c r="AA2" s="343"/>
+      <c r="AB2" s="343"/>
+      <c r="AC2" s="344"/>
+      <c r="AD2" s="345" t="s">
         <v>18</v>
       </c>
-      <c r="AE2" s="316"/>
-      <c r="AF2" s="316"/>
-      <c r="AG2" s="316"/>
-      <c r="AH2" s="316"/>
-      <c r="AI2" s="308"/>
-      <c r="AJ2" s="310" t="s">
+      <c r="AE2" s="346"/>
+      <c r="AF2" s="346"/>
+      <c r="AG2" s="346"/>
+      <c r="AH2" s="346"/>
+      <c r="AI2" s="338"/>
+      <c r="AJ2" s="340" t="s">
         <v>19</v>
       </c>
-      <c r="AK2" s="316"/>
-      <c r="AL2" s="316"/>
-      <c r="AM2" s="316"/>
-      <c r="AN2" s="316"/>
-      <c r="AO2" s="317"/>
-      <c r="AP2" s="303" t="s">
+      <c r="AK2" s="346"/>
+      <c r="AL2" s="346"/>
+      <c r="AM2" s="346"/>
+      <c r="AN2" s="346"/>
+      <c r="AO2" s="347"/>
+      <c r="AP2" s="333" t="s">
         <v>20</v>
       </c>
-      <c r="AQ2" s="304"/>
-      <c r="AR2" s="305"/>
-      <c r="AS2" s="305"/>
-      <c r="AT2" s="306"/>
-      <c r="AU2" s="306"/>
-      <c r="AV2" s="315" t="s">
+      <c r="AQ2" s="334"/>
+      <c r="AR2" s="335"/>
+      <c r="AS2" s="335"/>
+      <c r="AT2" s="336"/>
+      <c r="AU2" s="336"/>
+      <c r="AV2" s="345" t="s">
         <v>21</v>
       </c>
-      <c r="AW2" s="316"/>
-      <c r="AX2" s="316"/>
-      <c r="AY2" s="316"/>
-      <c r="AZ2" s="316"/>
-      <c r="BA2" s="317"/>
-      <c r="BB2" s="316" t="s">
+      <c r="AW2" s="346"/>
+      <c r="AX2" s="346"/>
+      <c r="AY2" s="346"/>
+      <c r="AZ2" s="346"/>
+      <c r="BA2" s="347"/>
+      <c r="BB2" s="346" t="s">
         <v>22</v>
       </c>
-      <c r="BC2" s="316"/>
-      <c r="BD2" s="317"/>
-      <c r="BE2" s="318" t="s">
+      <c r="BC2" s="346"/>
+      <c r="BD2" s="347"/>
+      <c r="BE2" s="348" t="s">
         <v>23</v>
       </c>
-      <c r="BF2" s="319"/>
-      <c r="BG2" s="320"/>
-      <c r="BH2" s="319" t="s">
+      <c r="BF2" s="349"/>
+      <c r="BG2" s="350"/>
+      <c r="BH2" s="349" t="s">
         <v>24</v>
       </c>
-      <c r="BI2" s="319"/>
-      <c r="BJ2" s="319"/>
-      <c r="BK2" s="319"/>
-      <c r="BL2" s="319"/>
-      <c r="BM2" s="319"/>
-      <c r="BN2" s="319"/>
-      <c r="BO2" s="319"/>
-      <c r="BP2" s="321"/>
-    </row>
-    <row r="3" spans="1:68">
-      <c r="I3" s="282" t="s">
+      <c r="BI2" s="349"/>
+      <c r="BJ2" s="349"/>
+      <c r="BK2" s="349"/>
+      <c r="BL2" s="349"/>
+      <c r="BM2" s="349"/>
+      <c r="BN2" s="349"/>
+      <c r="BO2" s="349"/>
+      <c r="BP2" s="351"/>
+    </row>
+    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="I3" s="298" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="283"/>
-      <c r="K3" s="284"/>
-      <c r="L3" s="282" t="s">
+      <c r="J3" s="299"/>
+      <c r="K3" s="296"/>
+      <c r="L3" s="298" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="283"/>
-      <c r="N3" s="284"/>
-      <c r="O3" s="284" t="s">
+      <c r="M3" s="299"/>
+      <c r="N3" s="296"/>
+      <c r="O3" s="296" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="285"/>
-      <c r="Q3" s="285"/>
-      <c r="R3" s="282" t="s">
+      <c r="P3" s="297"/>
+      <c r="Q3" s="297"/>
+      <c r="R3" s="298" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="283"/>
-      <c r="T3" s="284"/>
-      <c r="U3" s="284" t="s">
+      <c r="S3" s="299"/>
+      <c r="T3" s="296"/>
+      <c r="U3" s="296" t="s">
         <v>29</v>
       </c>
-      <c r="V3" s="285"/>
-      <c r="W3" s="286"/>
-      <c r="X3" s="349" t="s">
+      <c r="V3" s="297"/>
+      <c r="W3" s="306"/>
+      <c r="X3" s="307" t="s">
         <v>30</v>
       </c>
-      <c r="Y3" s="350"/>
-      <c r="Z3" s="348"/>
-      <c r="AA3" s="345" t="s">
+      <c r="Y3" s="308"/>
+      <c r="Z3" s="305"/>
+      <c r="AA3" s="300" t="s">
         <v>31</v>
       </c>
-      <c r="AB3" s="346"/>
-      <c r="AC3" s="347"/>
-      <c r="AD3" s="326" t="s">
+      <c r="AB3" s="301"/>
+      <c r="AC3" s="302"/>
+      <c r="AD3" s="303" t="s">
         <v>32</v>
       </c>
-      <c r="AE3" s="326"/>
-      <c r="AF3" s="325"/>
-      <c r="AG3" s="348" t="s">
+      <c r="AE3" s="303"/>
+      <c r="AF3" s="304"/>
+      <c r="AG3" s="305" t="s">
         <v>33</v>
       </c>
-      <c r="AH3" s="348"/>
-      <c r="AI3" s="348"/>
-      <c r="AJ3" s="284" t="s">
+      <c r="AH3" s="305"/>
+      <c r="AI3" s="305"/>
+      <c r="AJ3" s="296" t="s">
         <v>34</v>
       </c>
-      <c r="AK3" s="284"/>
-      <c r="AL3" s="284"/>
-      <c r="AM3" s="284" t="s">
+      <c r="AK3" s="296"/>
+      <c r="AL3" s="296"/>
+      <c r="AM3" s="296" t="s">
         <v>35</v>
       </c>
-      <c r="AN3" s="285"/>
-      <c r="AO3" s="286"/>
-      <c r="AP3" s="282" t="s">
+      <c r="AN3" s="297"/>
+      <c r="AO3" s="306"/>
+      <c r="AP3" s="298" t="s">
         <v>36</v>
       </c>
-      <c r="AQ3" s="283"/>
-      <c r="AR3" s="284"/>
-      <c r="AS3" s="284" t="s">
+      <c r="AQ3" s="299"/>
+      <c r="AR3" s="296"/>
+      <c r="AS3" s="296" t="s">
         <v>37</v>
       </c>
-      <c r="AT3" s="285"/>
-      <c r="AU3" s="285"/>
-      <c r="AV3" s="282" t="s">
+      <c r="AT3" s="297"/>
+      <c r="AU3" s="297"/>
+      <c r="AV3" s="298" t="s">
         <v>38</v>
       </c>
-      <c r="AW3" s="283"/>
-      <c r="AX3" s="284"/>
-      <c r="AY3" s="284" t="s">
+      <c r="AW3" s="299"/>
+      <c r="AX3" s="296"/>
+      <c r="AY3" s="296" t="s">
         <v>39</v>
       </c>
-      <c r="AZ3" s="285"/>
-      <c r="BA3" s="286"/>
-      <c r="BB3" s="283" t="s">
+      <c r="AZ3" s="297"/>
+      <c r="BA3" s="306"/>
+      <c r="BB3" s="299" t="s">
         <v>40</v>
       </c>
-      <c r="BC3" s="328"/>
-      <c r="BD3" s="286"/>
-      <c r="BE3" s="329" t="s">
+      <c r="BC3" s="313"/>
+      <c r="BD3" s="306"/>
+      <c r="BE3" s="314" t="s">
         <v>41</v>
       </c>
-      <c r="BF3" s="330"/>
-      <c r="BG3" s="324"/>
-      <c r="BH3" s="331" t="s">
+      <c r="BF3" s="315"/>
+      <c r="BG3" s="311"/>
+      <c r="BH3" s="316" t="s">
         <v>42</v>
       </c>
-      <c r="BI3" s="331"/>
-      <c r="BJ3" s="322"/>
-      <c r="BK3" s="322" t="s">
+      <c r="BI3" s="316"/>
+      <c r="BJ3" s="309"/>
+      <c r="BK3" s="309" t="s">
         <v>43</v>
       </c>
-      <c r="BL3" s="323"/>
-      <c r="BM3" s="324"/>
-      <c r="BN3" s="325" t="s">
+      <c r="BL3" s="310"/>
+      <c r="BM3" s="311"/>
+      <c r="BN3" s="304" t="s">
         <v>44</v>
       </c>
-      <c r="BO3" s="326"/>
-      <c r="BP3" s="327"/>
-    </row>
-    <row r="4" spans="1:68">
-      <c r="I4" s="332" t="s">
+      <c r="BO3" s="303"/>
+      <c r="BP3" s="312"/>
+    </row>
+    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="I4" s="287" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="333"/>
-      <c r="K4" s="334"/>
-      <c r="L4" s="334" t="s">
+      <c r="J4" s="288"/>
+      <c r="K4" s="284"/>
+      <c r="L4" s="284" t="s">
         <v>46</v>
       </c>
-      <c r="M4" s="334"/>
-      <c r="N4" s="334"/>
-      <c r="O4" s="334" t="s">
+      <c r="M4" s="284"/>
+      <c r="N4" s="284"/>
+      <c r="O4" s="284" t="s">
         <v>47</v>
       </c>
-      <c r="P4" s="335"/>
-      <c r="Q4" s="335"/>
-      <c r="R4" s="332" t="s">
+      <c r="P4" s="285"/>
+      <c r="Q4" s="285"/>
+      <c r="R4" s="287" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="333"/>
-      <c r="T4" s="334"/>
-      <c r="U4" s="334" t="s">
+      <c r="S4" s="288"/>
+      <c r="T4" s="284"/>
+      <c r="U4" s="284" t="s">
         <v>49</v>
       </c>
-      <c r="V4" s="335"/>
-      <c r="W4" s="336"/>
-      <c r="X4" s="337" t="s">
+      <c r="V4" s="285"/>
+      <c r="W4" s="286"/>
+      <c r="X4" s="290" t="s">
         <v>50</v>
       </c>
-      <c r="Y4" s="338"/>
-      <c r="Z4" s="339"/>
-      <c r="AA4" s="340" t="s">
+      <c r="Y4" s="280"/>
+      <c r="Z4" s="283"/>
+      <c r="AA4" s="291" t="s">
         <v>51</v>
       </c>
-      <c r="AB4" s="341"/>
-      <c r="AC4" s="342"/>
-      <c r="AD4" s="343" t="s">
+      <c r="AB4" s="292"/>
+      <c r="AC4" s="293"/>
+      <c r="AD4" s="294" t="s">
         <v>52</v>
       </c>
-      <c r="AE4" s="343"/>
-      <c r="AF4" s="344"/>
-      <c r="AG4" s="339" t="s">
+      <c r="AE4" s="294"/>
+      <c r="AF4" s="295"/>
+      <c r="AG4" s="283" t="s">
         <v>53</v>
       </c>
-      <c r="AH4" s="339"/>
-      <c r="AI4" s="339"/>
-      <c r="AJ4" s="334" t="s">
+      <c r="AH4" s="283"/>
+      <c r="AI4" s="283"/>
+      <c r="AJ4" s="284" t="s">
         <v>54</v>
       </c>
-      <c r="AK4" s="334"/>
-      <c r="AL4" s="334"/>
-      <c r="AM4" s="334" t="s">
+      <c r="AK4" s="284"/>
+      <c r="AL4" s="284"/>
+      <c r="AM4" s="284" t="s">
         <v>55</v>
       </c>
-      <c r="AN4" s="335"/>
-      <c r="AO4" s="336"/>
-      <c r="AP4" s="332" t="s">
+      <c r="AN4" s="285"/>
+      <c r="AO4" s="286"/>
+      <c r="AP4" s="287" t="s">
         <v>56</v>
       </c>
-      <c r="AQ4" s="333"/>
-      <c r="AR4" s="334"/>
-      <c r="AS4" s="334" t="s">
+      <c r="AQ4" s="288"/>
+      <c r="AR4" s="284"/>
+      <c r="AS4" s="284" t="s">
         <v>57</v>
       </c>
-      <c r="AT4" s="335"/>
-      <c r="AU4" s="335"/>
-      <c r="AV4" s="332" t="s">
+      <c r="AT4" s="285"/>
+      <c r="AU4" s="285"/>
+      <c r="AV4" s="287" t="s">
         <v>58</v>
       </c>
-      <c r="AW4" s="333"/>
-      <c r="AX4" s="334"/>
-      <c r="AY4" s="334" t="s">
+      <c r="AW4" s="288"/>
+      <c r="AX4" s="284"/>
+      <c r="AY4" s="284" t="s">
         <v>59</v>
       </c>
-      <c r="AZ4" s="335"/>
-      <c r="BA4" s="336"/>
-      <c r="BB4" s="333" t="s">
+      <c r="AZ4" s="285"/>
+      <c r="BA4" s="286"/>
+      <c r="BB4" s="288" t="s">
         <v>60</v>
       </c>
-      <c r="BC4" s="353"/>
-      <c r="BD4" s="336"/>
-      <c r="BE4" s="332" t="s">
+      <c r="BC4" s="289"/>
+      <c r="BD4" s="286"/>
+      <c r="BE4" s="287" t="s">
         <v>61</v>
       </c>
-      <c r="BF4" s="353"/>
-      <c r="BG4" s="336"/>
-      <c r="BH4" s="333" t="s">
+      <c r="BF4" s="289"/>
+      <c r="BG4" s="286"/>
+      <c r="BH4" s="288" t="s">
         <v>62</v>
       </c>
-      <c r="BI4" s="333"/>
-      <c r="BJ4" s="334"/>
-      <c r="BK4" s="334" t="s">
+      <c r="BI4" s="288"/>
+      <c r="BJ4" s="284"/>
+      <c r="BK4" s="284" t="s">
         <v>63</v>
       </c>
-      <c r="BL4" s="335"/>
-      <c r="BM4" s="336"/>
-      <c r="BN4" s="338" t="s">
+      <c r="BL4" s="285"/>
+      <c r="BM4" s="286"/>
+      <c r="BN4" s="280" t="s">
         <v>64</v>
       </c>
-      <c r="BO4" s="351"/>
-      <c r="BP4" s="352"/>
-    </row>
-    <row r="5" spans="1:68" ht="42">
+      <c r="BO4" s="281"/>
+      <c r="BP4" s="282"/>
+    </row>
+    <row r="5" spans="1:68" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>264</v>
       </c>
@@ -5804,7 +5815,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:68">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -6071,7 +6082,7 @@
         <v>368.5</v>
       </c>
     </row>
-    <row r="7" spans="1:68" ht="25">
+    <row r="7" spans="1:68" ht="27" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -6337,7 +6348,7 @@
         <v>181.5</v>
       </c>
     </row>
-    <row r="8" spans="1:68">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A8" s="179">
         <v>3</v>
       </c>
@@ -6604,7 +6615,7 @@
         <v>147.94520547945206</v>
       </c>
     </row>
-    <row r="9" spans="1:68">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A9" s="179">
         <v>4</v>
       </c>
@@ -6871,7 +6882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A10" s="179">
         <v>5</v>
       </c>
@@ -7138,7 +7149,7 @@
         <v>26.470588235294116</v>
       </c>
     </row>
-    <row r="11" spans="1:68">
+    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A11" s="179">
         <v>6</v>
       </c>
@@ -7405,7 +7416,7 @@
         <v>90.671641791044777</v>
       </c>
     </row>
-    <row r="12" spans="1:68">
+    <row r="12" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A12" s="179">
         <v>7</v>
       </c>
@@ -7672,7 +7683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:68">
+    <row r="13" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A13" s="179">
         <v>8</v>
       </c>
@@ -7939,7 +7950,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="14" spans="1:68">
+    <row r="14" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A14" s="179">
         <v>9</v>
       </c>
@@ -8026,7 +8037,7 @@
       <c r="BO14" s="174"/>
       <c r="BP14" s="159"/>
     </row>
-    <row r="15" spans="1:68">
+    <row r="15" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A15" s="179">
         <v>10</v>
       </c>
@@ -8273,7 +8284,7 @@
         <v>157.82608695652175</v>
       </c>
     </row>
-    <row r="16" spans="1:68">
+    <row r="16" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A16" s="179">
         <v>11</v>
       </c>
@@ -8520,7 +8531,7 @@
         <v>288.75</v>
       </c>
     </row>
-    <row r="17" spans="1:68">
+    <row r="17" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A17" s="179">
         <v>12</v>
       </c>
@@ -8767,7 +8778,7 @@
         <v>93.612871769868363</v>
       </c>
     </row>
-    <row r="18" spans="1:68" ht="25">
+    <row r="18" spans="1:68" ht="27" x14ac:dyDescent="0.25">
       <c r="A18" s="179">
         <v>13</v>
       </c>
@@ -9034,7 +9045,7 @@
         <v>98.181818181818187</v>
       </c>
     </row>
-    <row r="19" spans="1:68" ht="14.5" thickBot="1">
+    <row r="19" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>14</v>
       </c>
@@ -9121,7 +9132,7 @@
       <c r="BO19" s="174"/>
       <c r="BP19" s="159"/>
     </row>
-    <row r="20" spans="1:68" ht="14.5" thickBot="1">
+    <row r="20" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>15</v>
       </c>
@@ -9208,7 +9219,7 @@
       <c r="BO20" s="174"/>
       <c r="BP20" s="159"/>
     </row>
-    <row r="21" spans="1:68" ht="14.5" thickBot="1">
+    <row r="21" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="180">
         <v>16</v>
       </c>
@@ -9295,7 +9306,7 @@
       <c r="BO21" s="174"/>
       <c r="BP21" s="193"/>
     </row>
-    <row r="22" spans="1:68" ht="14.5" thickBot="1">
+    <row r="22" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="180">
         <v>17</v>
       </c>
@@ -9382,7 +9393,7 @@
       <c r="BO22" s="174"/>
       <c r="BP22" s="193"/>
     </row>
-    <row r="23" spans="1:68" ht="14.5" thickBot="1">
+    <row r="23" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="180">
         <v>18</v>
       </c>
@@ -9469,7 +9480,7 @@
       <c r="BO23" s="174"/>
       <c r="BP23" s="193"/>
     </row>
-    <row r="24" spans="1:68" ht="14.5" thickBot="1">
+    <row r="24" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="180">
         <v>19</v>
       </c>
@@ -9556,7 +9567,7 @@
       <c r="BO24" s="174"/>
       <c r="BP24" s="193"/>
     </row>
-    <row r="25" spans="1:68" ht="14.5" thickBot="1">
+    <row r="25" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="180">
         <v>20</v>
       </c>
@@ -9643,7 +9654,7 @@
       <c r="BO25" s="174"/>
       <c r="BP25" s="193"/>
     </row>
-    <row r="26" spans="1:68" ht="14.5" thickBot="1">
+    <row r="26" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="180">
         <v>21</v>
       </c>
@@ -9730,7 +9741,7 @@
       <c r="BO26" s="174"/>
       <c r="BP26" s="193"/>
     </row>
-    <row r="27" spans="1:68" ht="25">
+    <row r="27" spans="1:68" ht="27" x14ac:dyDescent="0.25">
       <c r="A27" s="180">
         <v>22</v>
       </c>
@@ -9995,7 +10006,7 @@
         <v>1105.0000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:68" s="162" customFormat="1">
+    <row r="28" spans="1:68" s="162" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F28" s="163"/>
       <c r="G28" s="164" t="s">
         <v>217</v>
@@ -10182,7 +10193,7 @@
         <v>1520.9582124139995</v>
       </c>
     </row>
-    <row r="29" spans="1:68">
+    <row r="29" spans="1:68" x14ac:dyDescent="0.25">
       <c r="F29" s="75"/>
       <c r="G29" s="160" t="s">
         <v>155</v>
@@ -10309,7 +10320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:68">
+    <row r="31" spans="1:68" x14ac:dyDescent="0.25">
       <c r="H31">
         <f>SUM(H6:H27)</f>
         <v>90000</v>
@@ -10317,41 +10328,11 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="BN4:BP4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AL4"/>
-    <mergeCell ref="AM4:AO4"/>
-    <mergeCell ref="AP4:AR4"/>
-    <mergeCell ref="AS4:AU4"/>
-    <mergeCell ref="AV4:AX4"/>
-    <mergeCell ref="AY4:BA4"/>
-    <mergeCell ref="BB4:BD4"/>
-    <mergeCell ref="BE4:BG4"/>
-    <mergeCell ref="BH4:BJ4"/>
-    <mergeCell ref="BK4:BM4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AS3:AU3"/>
-    <mergeCell ref="AV3:AX3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="BK3:BM3"/>
-    <mergeCell ref="BN3:BP3"/>
-    <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="BE3:BG3"/>
-    <mergeCell ref="BH3:BJ3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="U3:W3"/>
     <mergeCell ref="I1:W1"/>
     <mergeCell ref="X1:AO1"/>
     <mergeCell ref="AP1:BD1"/>
@@ -10366,11 +10347,41 @@
     <mergeCell ref="BB2:BD2"/>
     <mergeCell ref="BE2:BG2"/>
     <mergeCell ref="BH2:BP2"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="AY3:BA3"/>
+    <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="BE3:BG3"/>
+    <mergeCell ref="BH3:BJ3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AV3:AX3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="BN4:BP4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AL4"/>
+    <mergeCell ref="AM4:AO4"/>
+    <mergeCell ref="AP4:AR4"/>
+    <mergeCell ref="AS4:AU4"/>
+    <mergeCell ref="AV4:AX4"/>
+    <mergeCell ref="AY4:BA4"/>
+    <mergeCell ref="BB4:BD4"/>
+    <mergeCell ref="BE4:BG4"/>
+    <mergeCell ref="BH4:BJ4"/>
+    <mergeCell ref="BK4:BM4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10379,430 +10390,430 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6489654-22F9-4ED4-BDC6-86CD0FC0849C}">
   <dimension ref="A1:BM23"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="5" width="33.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="4" width="19.7109375" customWidth="1"/>
+    <col min="5" max="5" width="33.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" ht="14.5" thickBot="1">
-      <c r="F1" s="287" t="s">
+    <row r="1" spans="1:65" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F1" s="317" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="288"/>
-      <c r="H1" s="289"/>
-      <c r="I1" s="289"/>
-      <c r="J1" s="289"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
-      <c r="M1" s="289"/>
-      <c r="N1" s="289"/>
-      <c r="O1" s="289"/>
-      <c r="P1" s="289"/>
-      <c r="Q1" s="289"/>
-      <c r="R1" s="289"/>
-      <c r="S1" s="290"/>
-      <c r="T1" s="291"/>
-      <c r="U1" s="292" t="s">
+      <c r="G1" s="318"/>
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
+      <c r="M1" s="319"/>
+      <c r="N1" s="319"/>
+      <c r="O1" s="319"/>
+      <c r="P1" s="319"/>
+      <c r="Q1" s="319"/>
+      <c r="R1" s="319"/>
+      <c r="S1" s="320"/>
+      <c r="T1" s="321"/>
+      <c r="U1" s="322" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="293"/>
-      <c r="W1" s="293"/>
-      <c r="X1" s="293"/>
-      <c r="Y1" s="293"/>
-      <c r="Z1" s="293"/>
-      <c r="AA1" s="293"/>
-      <c r="AB1" s="293"/>
-      <c r="AC1" s="293"/>
-      <c r="AD1" s="293"/>
-      <c r="AE1" s="293"/>
-      <c r="AF1" s="293"/>
-      <c r="AG1" s="293"/>
-      <c r="AH1" s="293"/>
-      <c r="AI1" s="293"/>
-      <c r="AJ1" s="293"/>
-      <c r="AK1" s="293"/>
-      <c r="AL1" s="294"/>
-      <c r="AM1" s="295" t="s">
+      <c r="V1" s="323"/>
+      <c r="W1" s="323"/>
+      <c r="X1" s="323"/>
+      <c r="Y1" s="323"/>
+      <c r="Z1" s="323"/>
+      <c r="AA1" s="323"/>
+      <c r="AB1" s="323"/>
+      <c r="AC1" s="323"/>
+      <c r="AD1" s="323"/>
+      <c r="AE1" s="323"/>
+      <c r="AF1" s="323"/>
+      <c r="AG1" s="323"/>
+      <c r="AH1" s="323"/>
+      <c r="AI1" s="323"/>
+      <c r="AJ1" s="323"/>
+      <c r="AK1" s="323"/>
+      <c r="AL1" s="324"/>
+      <c r="AM1" s="325" t="s">
         <v>13</v>
       </c>
-      <c r="AN1" s="296"/>
-      <c r="AO1" s="297"/>
-      <c r="AP1" s="297"/>
-      <c r="AQ1" s="297"/>
-      <c r="AR1" s="297"/>
-      <c r="AS1" s="297"/>
-      <c r="AT1" s="297"/>
-      <c r="AU1" s="297"/>
-      <c r="AV1" s="297"/>
-      <c r="AW1" s="297"/>
-      <c r="AX1" s="297"/>
-      <c r="AY1" s="297"/>
-      <c r="AZ1" s="298"/>
-      <c r="BA1" s="299"/>
-      <c r="BB1" s="300" t="s">
+      <c r="AN1" s="326"/>
+      <c r="AO1" s="327"/>
+      <c r="AP1" s="327"/>
+      <c r="AQ1" s="327"/>
+      <c r="AR1" s="327"/>
+      <c r="AS1" s="327"/>
+      <c r="AT1" s="327"/>
+      <c r="AU1" s="327"/>
+      <c r="AV1" s="327"/>
+      <c r="AW1" s="327"/>
+      <c r="AX1" s="327"/>
+      <c r="AY1" s="327"/>
+      <c r="AZ1" s="328"/>
+      <c r="BA1" s="329"/>
+      <c r="BB1" s="330" t="s">
         <v>14</v>
       </c>
-      <c r="BC1" s="301"/>
-      <c r="BD1" s="301"/>
-      <c r="BE1" s="301"/>
-      <c r="BF1" s="301"/>
-      <c r="BG1" s="301"/>
-      <c r="BH1" s="301"/>
-      <c r="BI1" s="301"/>
-      <c r="BJ1" s="301"/>
-      <c r="BK1" s="301"/>
-      <c r="BL1" s="301"/>
-      <c r="BM1" s="302"/>
-    </row>
-    <row r="2" spans="1:65" ht="14.5" thickBot="1">
-      <c r="F2" s="303" t="s">
+      <c r="BC1" s="331"/>
+      <c r="BD1" s="331"/>
+      <c r="BE1" s="331"/>
+      <c r="BF1" s="331"/>
+      <c r="BG1" s="331"/>
+      <c r="BH1" s="331"/>
+      <c r="BI1" s="331"/>
+      <c r="BJ1" s="331"/>
+      <c r="BK1" s="331"/>
+      <c r="BL1" s="331"/>
+      <c r="BM1" s="332"/>
+    </row>
+    <row r="2" spans="1:65" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="333" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="304"/>
-      <c r="H2" s="305"/>
-      <c r="I2" s="305"/>
-      <c r="J2" s="305"/>
-      <c r="K2" s="305"/>
-      <c r="L2" s="305"/>
-      <c r="M2" s="306"/>
-      <c r="N2" s="306"/>
-      <c r="O2" s="307" t="s">
+      <c r="G2" s="334"/>
+      <c r="H2" s="335"/>
+      <c r="I2" s="335"/>
+      <c r="J2" s="335"/>
+      <c r="K2" s="335"/>
+      <c r="L2" s="335"/>
+      <c r="M2" s="336"/>
+      <c r="N2" s="336"/>
+      <c r="O2" s="337" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="308"/>
-      <c r="Q2" s="309"/>
-      <c r="R2" s="309"/>
-      <c r="S2" s="310"/>
-      <c r="T2" s="311"/>
-      <c r="U2" s="312" t="s">
+      <c r="P2" s="338"/>
+      <c r="Q2" s="339"/>
+      <c r="R2" s="339"/>
+      <c r="S2" s="340"/>
+      <c r="T2" s="341"/>
+      <c r="U2" s="342" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="313"/>
-      <c r="W2" s="313"/>
-      <c r="X2" s="313"/>
-      <c r="Y2" s="313"/>
-      <c r="Z2" s="314"/>
-      <c r="AA2" s="315" t="s">
+      <c r="V2" s="343"/>
+      <c r="W2" s="343"/>
+      <c r="X2" s="343"/>
+      <c r="Y2" s="343"/>
+      <c r="Z2" s="344"/>
+      <c r="AA2" s="345" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" s="316"/>
-      <c r="AC2" s="316"/>
-      <c r="AD2" s="316"/>
-      <c r="AE2" s="316"/>
-      <c r="AF2" s="308"/>
-      <c r="AG2" s="310" t="s">
+      <c r="AB2" s="346"/>
+      <c r="AC2" s="346"/>
+      <c r="AD2" s="346"/>
+      <c r="AE2" s="346"/>
+      <c r="AF2" s="338"/>
+      <c r="AG2" s="340" t="s">
         <v>19</v>
       </c>
-      <c r="AH2" s="316"/>
-      <c r="AI2" s="316"/>
-      <c r="AJ2" s="316"/>
-      <c r="AK2" s="316"/>
-      <c r="AL2" s="317"/>
-      <c r="AM2" s="303" t="s">
+      <c r="AH2" s="346"/>
+      <c r="AI2" s="346"/>
+      <c r="AJ2" s="346"/>
+      <c r="AK2" s="346"/>
+      <c r="AL2" s="347"/>
+      <c r="AM2" s="333" t="s">
         <v>20</v>
       </c>
-      <c r="AN2" s="304"/>
-      <c r="AO2" s="305"/>
-      <c r="AP2" s="305"/>
-      <c r="AQ2" s="306"/>
-      <c r="AR2" s="306"/>
-      <c r="AS2" s="315" t="s">
+      <c r="AN2" s="334"/>
+      <c r="AO2" s="335"/>
+      <c r="AP2" s="335"/>
+      <c r="AQ2" s="336"/>
+      <c r="AR2" s="336"/>
+      <c r="AS2" s="345" t="s">
         <v>21</v>
       </c>
-      <c r="AT2" s="316"/>
-      <c r="AU2" s="316"/>
-      <c r="AV2" s="316"/>
-      <c r="AW2" s="316"/>
-      <c r="AX2" s="317"/>
-      <c r="AY2" s="315" t="s">
+      <c r="AT2" s="346"/>
+      <c r="AU2" s="346"/>
+      <c r="AV2" s="346"/>
+      <c r="AW2" s="346"/>
+      <c r="AX2" s="347"/>
+      <c r="AY2" s="345" t="s">
         <v>22</v>
       </c>
-      <c r="AZ2" s="316"/>
-      <c r="BA2" s="317"/>
-      <c r="BB2" s="383" t="s">
+      <c r="AZ2" s="346"/>
+      <c r="BA2" s="347"/>
+      <c r="BB2" s="352" t="s">
         <v>23</v>
       </c>
-      <c r="BC2" s="319"/>
-      <c r="BD2" s="321"/>
-      <c r="BE2" s="319" t="s">
+      <c r="BC2" s="349"/>
+      <c r="BD2" s="351"/>
+      <c r="BE2" s="349" t="s">
         <v>24</v>
       </c>
-      <c r="BF2" s="319"/>
-      <c r="BG2" s="319"/>
-      <c r="BH2" s="319"/>
-      <c r="BI2" s="319"/>
-      <c r="BJ2" s="319"/>
-      <c r="BK2" s="319"/>
-      <c r="BL2" s="319"/>
-      <c r="BM2" s="321"/>
-    </row>
-    <row r="3" spans="1:65">
-      <c r="F3" s="354" t="s">
+      <c r="BF2" s="349"/>
+      <c r="BG2" s="349"/>
+      <c r="BH2" s="349"/>
+      <c r="BI2" s="349"/>
+      <c r="BJ2" s="349"/>
+      <c r="BK2" s="349"/>
+      <c r="BL2" s="349"/>
+      <c r="BM2" s="351"/>
+    </row>
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="F3" s="358" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="355"/>
-      <c r="H3" s="356"/>
-      <c r="I3" s="354" t="s">
+      <c r="H3" s="357"/>
+      <c r="I3" s="358" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="355"/>
-      <c r="K3" s="360"/>
-      <c r="L3" s="362" t="s">
+      <c r="K3" s="356"/>
+      <c r="L3" s="354" t="s">
         <v>27</v>
       </c>
       <c r="M3" s="355"/>
-      <c r="N3" s="356"/>
-      <c r="O3" s="354" t="s">
+      <c r="N3" s="357"/>
+      <c r="O3" s="358" t="s">
         <v>28</v>
       </c>
       <c r="P3" s="355"/>
-      <c r="Q3" s="360"/>
-      <c r="R3" s="362" t="s">
+      <c r="Q3" s="356"/>
+      <c r="R3" s="354" t="s">
         <v>29</v>
       </c>
       <c r="S3" s="355"/>
-      <c r="T3" s="356"/>
-      <c r="U3" s="367" t="s">
+      <c r="T3" s="357"/>
+      <c r="U3" s="360" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="326"/>
-      <c r="W3" s="325"/>
-      <c r="X3" s="374" t="s">
+      <c r="V3" s="303"/>
+      <c r="W3" s="304"/>
+      <c r="X3" s="379" t="s">
         <v>31</v>
       </c>
-      <c r="Y3" s="375"/>
-      <c r="Z3" s="376"/>
-      <c r="AA3" s="377" t="s">
+      <c r="Y3" s="380"/>
+      <c r="Z3" s="381"/>
+      <c r="AA3" s="353" t="s">
         <v>32</v>
       </c>
-      <c r="AB3" s="326"/>
-      <c r="AC3" s="325"/>
-      <c r="AD3" s="377" t="s">
+      <c r="AB3" s="303"/>
+      <c r="AC3" s="304"/>
+      <c r="AD3" s="353" t="s">
         <v>33</v>
       </c>
-      <c r="AE3" s="326"/>
-      <c r="AF3" s="325"/>
-      <c r="AG3" s="362" t="s">
+      <c r="AE3" s="303"/>
+      <c r="AF3" s="304"/>
+      <c r="AG3" s="354" t="s">
         <v>34</v>
       </c>
       <c r="AH3" s="355"/>
-      <c r="AI3" s="360"/>
-      <c r="AJ3" s="362" t="s">
+      <c r="AI3" s="356"/>
+      <c r="AJ3" s="354" t="s">
         <v>35</v>
       </c>
       <c r="AK3" s="355"/>
-      <c r="AL3" s="356"/>
-      <c r="AM3" s="354" t="s">
+      <c r="AL3" s="357"/>
+      <c r="AM3" s="358" t="s">
         <v>36</v>
       </c>
       <c r="AN3" s="355"/>
-      <c r="AO3" s="360"/>
-      <c r="AP3" s="362" t="s">
+      <c r="AO3" s="356"/>
+      <c r="AP3" s="354" t="s">
         <v>37</v>
       </c>
       <c r="AQ3" s="355"/>
-      <c r="AR3" s="356"/>
-      <c r="AS3" s="354" t="s">
+      <c r="AR3" s="357"/>
+      <c r="AS3" s="358" t="s">
         <v>38</v>
       </c>
       <c r="AT3" s="355"/>
-      <c r="AU3" s="360"/>
-      <c r="AV3" s="362" t="s">
+      <c r="AU3" s="356"/>
+      <c r="AV3" s="354" t="s">
         <v>39</v>
       </c>
       <c r="AW3" s="355"/>
-      <c r="AX3" s="356"/>
-      <c r="AY3" s="354" t="s">
+      <c r="AX3" s="357"/>
+      <c r="AY3" s="358" t="s">
         <v>40</v>
       </c>
       <c r="AZ3" s="355"/>
-      <c r="BA3" s="356"/>
-      <c r="BB3" s="382" t="s">
+      <c r="BA3" s="357"/>
+      <c r="BB3" s="362" t="s">
         <v>41</v>
       </c>
-      <c r="BC3" s="330"/>
-      <c r="BD3" s="380"/>
-      <c r="BE3" s="382" t="s">
+      <c r="BC3" s="315"/>
+      <c r="BD3" s="359"/>
+      <c r="BE3" s="362" t="s">
         <v>42</v>
       </c>
-      <c r="BF3" s="330"/>
-      <c r="BG3" s="331"/>
-      <c r="BH3" s="323" t="s">
+      <c r="BF3" s="315"/>
+      <c r="BG3" s="316"/>
+      <c r="BH3" s="310" t="s">
         <v>43</v>
       </c>
-      <c r="BI3" s="330"/>
-      <c r="BJ3" s="380"/>
-      <c r="BK3" s="367" t="s">
+      <c r="BI3" s="315"/>
+      <c r="BJ3" s="359"/>
+      <c r="BK3" s="360" t="s">
         <v>44</v>
       </c>
-      <c r="BL3" s="326"/>
-      <c r="BM3" s="381"/>
-    </row>
-    <row r="4" spans="1:65">
-      <c r="F4" s="357" t="s">
+      <c r="BL3" s="303"/>
+      <c r="BM3" s="361"/>
+    </row>
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="F4" s="372" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="358"/>
-      <c r="H4" s="359"/>
-      <c r="I4" s="361" t="s">
+      <c r="G4" s="369"/>
+      <c r="H4" s="370"/>
+      <c r="I4" s="368" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="358"/>
-      <c r="K4" s="359"/>
-      <c r="L4" s="361" t="s">
+      <c r="J4" s="369"/>
+      <c r="K4" s="370"/>
+      <c r="L4" s="368" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="358"/>
-      <c r="N4" s="363"/>
-      <c r="O4" s="357" t="s">
+      <c r="M4" s="369"/>
+      <c r="N4" s="371"/>
+      <c r="O4" s="372" t="s">
         <v>48</v>
       </c>
-      <c r="P4" s="358"/>
-      <c r="Q4" s="359"/>
-      <c r="R4" s="361" t="s">
+      <c r="P4" s="369"/>
+      <c r="Q4" s="370"/>
+      <c r="R4" s="368" t="s">
         <v>49</v>
       </c>
-      <c r="S4" s="358"/>
-      <c r="T4" s="363"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="369"/>
+      <c r="T4" s="371"/>
+      <c r="U4" s="363" t="s">
         <v>50</v>
       </c>
-      <c r="V4" s="369"/>
-      <c r="W4" s="370"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="367"/>
+      <c r="X4" s="376" t="s">
         <v>51</v>
       </c>
-      <c r="Y4" s="372"/>
-      <c r="Z4" s="373"/>
-      <c r="AA4" s="364" t="s">
+      <c r="Y4" s="377"/>
+      <c r="Z4" s="378"/>
+      <c r="AA4" s="373" t="s">
         <v>52</v>
       </c>
-      <c r="AB4" s="365"/>
-      <c r="AC4" s="366"/>
-      <c r="AD4" s="379" t="s">
+      <c r="AB4" s="374"/>
+      <c r="AC4" s="375"/>
+      <c r="AD4" s="366" t="s">
         <v>53</v>
       </c>
-      <c r="AE4" s="369"/>
-      <c r="AF4" s="370"/>
-      <c r="AG4" s="361" t="s">
+      <c r="AE4" s="364"/>
+      <c r="AF4" s="367"/>
+      <c r="AG4" s="368" t="s">
         <v>54</v>
       </c>
-      <c r="AH4" s="358"/>
-      <c r="AI4" s="359"/>
-      <c r="AJ4" s="361" t="s">
+      <c r="AH4" s="369"/>
+      <c r="AI4" s="370"/>
+      <c r="AJ4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="AK4" s="358"/>
-      <c r="AL4" s="363"/>
-      <c r="AM4" s="357" t="s">
+      <c r="AK4" s="369"/>
+      <c r="AL4" s="371"/>
+      <c r="AM4" s="372" t="s">
         <v>56</v>
       </c>
-      <c r="AN4" s="358"/>
-      <c r="AO4" s="359"/>
-      <c r="AP4" s="361" t="s">
+      <c r="AN4" s="369"/>
+      <c r="AO4" s="370"/>
+      <c r="AP4" s="368" t="s">
         <v>57</v>
       </c>
-      <c r="AQ4" s="358"/>
-      <c r="AR4" s="363"/>
-      <c r="AS4" s="357" t="s">
+      <c r="AQ4" s="369"/>
+      <c r="AR4" s="371"/>
+      <c r="AS4" s="372" t="s">
         <v>58</v>
       </c>
-      <c r="AT4" s="358"/>
-      <c r="AU4" s="359"/>
-      <c r="AV4" s="361" t="s">
+      <c r="AT4" s="369"/>
+      <c r="AU4" s="370"/>
+      <c r="AV4" s="368" t="s">
         <v>59</v>
       </c>
-      <c r="AW4" s="358"/>
-      <c r="AX4" s="363"/>
-      <c r="AY4" s="357" t="s">
+      <c r="AW4" s="369"/>
+      <c r="AX4" s="371"/>
+      <c r="AY4" s="372" t="s">
         <v>60</v>
       </c>
-      <c r="AZ4" s="358"/>
-      <c r="BA4" s="363"/>
-      <c r="BB4" s="357" t="s">
+      <c r="AZ4" s="369"/>
+      <c r="BA4" s="371"/>
+      <c r="BB4" s="372" t="s">
         <v>61</v>
       </c>
-      <c r="BC4" s="358"/>
-      <c r="BD4" s="363"/>
-      <c r="BE4" s="357" t="s">
+      <c r="BC4" s="369"/>
+      <c r="BD4" s="371"/>
+      <c r="BE4" s="372" t="s">
         <v>62</v>
       </c>
-      <c r="BF4" s="358"/>
-      <c r="BG4" s="359"/>
-      <c r="BH4" s="361" t="s">
+      <c r="BF4" s="369"/>
+      <c r="BG4" s="370"/>
+      <c r="BH4" s="368" t="s">
         <v>63</v>
       </c>
-      <c r="BI4" s="358"/>
-      <c r="BJ4" s="363"/>
-      <c r="BK4" s="368" t="s">
+      <c r="BI4" s="369"/>
+      <c r="BJ4" s="371"/>
+      <c r="BK4" s="363" t="s">
         <v>64</v>
       </c>
-      <c r="BL4" s="369"/>
-      <c r="BM4" s="378"/>
-    </row>
-    <row r="5" spans="1:65" ht="42">
+      <c r="BL4" s="364"/>
+      <c r="BM4" s="365"/>
+    </row>
+    <row r="5" spans="1:65" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>264</v>
       </c>
@@ -10999,7 +11010,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:65">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="180">
         <v>16</v>
       </c>
@@ -11079,7 +11090,7 @@
       <c r="BL6" s="174"/>
       <c r="BM6" s="159"/>
     </row>
-    <row r="7" spans="1:65">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="180">
         <v>17</v>
       </c>
@@ -11159,7 +11170,7 @@
       <c r="BL7" s="174"/>
       <c r="BM7" s="159"/>
     </row>
-    <row r="8" spans="1:65">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="180">
         <v>18</v>
       </c>
@@ -11239,7 +11250,7 @@
       <c r="BL8" s="174"/>
       <c r="BM8" s="159"/>
     </row>
-    <row r="9" spans="1:65">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="180">
         <v>19</v>
       </c>
@@ -11319,7 +11330,7 @@
       <c r="BL9" s="174"/>
       <c r="BM9" s="159"/>
     </row>
-    <row r="10" spans="1:65">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="180">
         <v>20</v>
       </c>
@@ -11399,7 +11410,7 @@
       <c r="BL10" s="174"/>
       <c r="BM10" s="159"/>
     </row>
-    <row r="11" spans="1:65">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" s="180">
         <v>21</v>
       </c>
@@ -11479,7 +11490,7 @@
       <c r="BL11" s="174"/>
       <c r="BM11" s="159"/>
     </row>
-    <row r="12" spans="1:65" s="162" customFormat="1">
+    <row r="12" spans="1:65" s="162" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F12" s="165"/>
       <c r="G12" s="170" t="e">
         <f>SUM(#REF!)</f>
@@ -11661,7 +11672,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:65">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="F13" s="160"/>
       <c r="G13" s="160"/>
       <c r="H13" s="161" t="e">
@@ -11783,8 +11794,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:65" ht="14.5" thickBot="1"/>
-    <row r="23" spans="1:65" ht="25">
+    <row r="22" spans="1:65" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:65" ht="27" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>12</v>
       </c>
@@ -11959,6 +11970,47 @@
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="BK4:BM4"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AL4"/>
+    <mergeCell ref="AM4:AO4"/>
+    <mergeCell ref="AP4:AR4"/>
+    <mergeCell ref="AS4:AU4"/>
+    <mergeCell ref="AV4:AX4"/>
+    <mergeCell ref="AY4:BA4"/>
+    <mergeCell ref="BB4:BD4"/>
+    <mergeCell ref="BE4:BG4"/>
+    <mergeCell ref="BH4:BJ4"/>
+    <mergeCell ref="BH3:BJ3"/>
+    <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AV3:AX3"/>
+    <mergeCell ref="AY3:BA3"/>
+    <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="BE3:BG3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AS2:AX2"/>
     <mergeCell ref="AY2:BA2"/>
     <mergeCell ref="BB2:BD2"/>
     <mergeCell ref="BE2:BM2"/>
@@ -11972,47 +12024,6 @@
     <mergeCell ref="AA2:AF2"/>
     <mergeCell ref="AG2:AL2"/>
     <mergeCell ref="AM2:AR2"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AL3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AS2:AX2"/>
-    <mergeCell ref="BH3:BJ3"/>
-    <mergeCell ref="BK3:BM3"/>
-    <mergeCell ref="AP3:AR3"/>
-    <mergeCell ref="AS3:AU3"/>
-    <mergeCell ref="AV3:AX3"/>
-    <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="BE3:BG3"/>
-    <mergeCell ref="BK4:BM4"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AL4"/>
-    <mergeCell ref="AM4:AO4"/>
-    <mergeCell ref="AP4:AR4"/>
-    <mergeCell ref="AS4:AU4"/>
-    <mergeCell ref="AV4:AX4"/>
-    <mergeCell ref="AY4:BA4"/>
-    <mergeCell ref="BB4:BD4"/>
-    <mergeCell ref="BE4:BG4"/>
-    <mergeCell ref="BH4:BJ4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="U3:W3"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="L4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12021,125 +12032,125 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D11F29-A766-477F-B75F-AE1A265D1AA1}">
   <dimension ref="A1:AA31"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.58203125" style="39" customWidth="1"/>
-    <col min="2" max="2" width="36.75" style="39" customWidth="1"/>
-    <col min="3" max="3" width="19.25" style="39" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" style="39" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" style="39" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="39" customWidth="1"/>
     <col min="4" max="4" width="9" style="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.75" style="39" customWidth="1"/>
-    <col min="6" max="6" width="11.4140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.75" style="39" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.4140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" style="39" customWidth="1"/>
-    <col min="11" max="11" width="15.75" style="39" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.75" style="39" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.58203125" style="39" customWidth="1"/>
-    <col min="14" max="14" width="13.58203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.25" style="39" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.25" style="39" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.58203125" style="39" customWidth="1"/>
-    <col min="18" max="18" width="13.1640625" style="39" customWidth="1"/>
-    <col min="19" max="19" width="13.4140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.58203125" style="39" customWidth="1"/>
-    <col min="21" max="21" width="13.4140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.25" style="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.75" style="39" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.25" style="39" customWidth="1"/>
-    <col min="26" max="26" width="15.25" style="39" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.1640625" style="39"/>
-    <col min="29" max="29" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.1640625" style="39"/>
+    <col min="5" max="5" width="10.7109375" style="39" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="39" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" style="39" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="39" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" style="39" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" style="39" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.5703125" style="39" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.28515625" style="39" customWidth="1"/>
+    <col min="26" max="26" width="15.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" style="39"/>
+    <col min="29" max="29" width="10.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="18.5" thickBot="1">
-      <c r="A1" s="384" t="s">
+    <row r="1" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="385" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="385"/>
-      <c r="C1" s="385"/>
-      <c r="D1" s="386"/>
+      <c r="B1" s="386"/>
+      <c r="C1" s="386"/>
+      <c r="D1" s="387"/>
       <c r="F1" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="287" t="s">
+      <c r="G1" s="317" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="289"/>
-      <c r="I1" s="289"/>
-      <c r="J1" s="289"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
-      <c r="M1" s="387" t="s">
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
+      <c r="M1" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="N1" s="387"/>
-      <c r="O1" s="387"/>
-      <c r="P1" s="387"/>
-      <c r="Q1" s="387"/>
-      <c r="R1" s="387"/>
-      <c r="S1" s="297" t="s">
+      <c r="N1" s="388"/>
+      <c r="O1" s="388"/>
+      <c r="P1" s="388"/>
+      <c r="Q1" s="388"/>
+      <c r="R1" s="388"/>
+      <c r="S1" s="327" t="s">
         <v>85</v>
       </c>
-      <c r="T1" s="297"/>
-      <c r="U1" s="297"/>
-      <c r="V1" s="297"/>
-      <c r="W1" s="297"/>
-      <c r="X1" s="388" t="s">
+      <c r="T1" s="327"/>
+      <c r="U1" s="327"/>
+      <c r="V1" s="327"/>
+      <c r="W1" s="327"/>
+      <c r="X1" s="389" t="s">
         <v>86</v>
       </c>
-      <c r="Y1" s="388"/>
-      <c r="Z1" s="388"/>
-      <c r="AA1" s="389" t="s">
+      <c r="Y1" s="389"/>
+      <c r="Z1" s="389"/>
+      <c r="AA1" s="382" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="14.5" thickBot="1">
+    <row r="2" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F2" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="303" t="s">
+      <c r="G2" s="333" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="305"/>
-      <c r="I2" s="305"/>
-      <c r="J2" s="305" t="s">
+      <c r="H2" s="335"/>
+      <c r="I2" s="335"/>
+      <c r="J2" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="K2" s="305"/>
-      <c r="L2" s="305"/>
-      <c r="M2" s="305" t="s">
+      <c r="K2" s="335"/>
+      <c r="L2" s="335"/>
+      <c r="M2" s="335" t="s">
         <v>91</v>
       </c>
-      <c r="N2" s="305"/>
-      <c r="O2" s="305"/>
-      <c r="P2" s="305" t="s">
+      <c r="N2" s="335"/>
+      <c r="O2" s="335"/>
+      <c r="P2" s="335" t="s">
         <v>92</v>
       </c>
-      <c r="Q2" s="305"/>
-      <c r="R2" s="305"/>
-      <c r="S2" s="305" t="s">
+      <c r="Q2" s="335"/>
+      <c r="R2" s="335"/>
+      <c r="S2" s="335" t="s">
         <v>93</v>
       </c>
-      <c r="T2" s="305"/>
-      <c r="U2" s="305" t="s">
+      <c r="T2" s="335"/>
+      <c r="U2" s="335" t="s">
         <v>94</v>
       </c>
-      <c r="V2" s="305"/>
-      <c r="W2" s="305"/>
+      <c r="V2" s="335"/>
+      <c r="W2" s="335"/>
       <c r="X2" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="Y2" s="391" t="s">
+      <c r="Y2" s="384" t="s">
         <v>96</v>
       </c>
-      <c r="Z2" s="391"/>
-      <c r="AA2" s="390"/>
-    </row>
-    <row r="3" spans="1:27" ht="14.5" thickBot="1">
+      <c r="Z2" s="384"/>
+      <c r="AA2" s="383"/>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F3" s="41" t="s">
         <v>97</v>
       </c>
@@ -12203,9 +12214,9 @@
       <c r="Z3" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="AA3" s="390"/>
-    </row>
-    <row r="4" spans="1:27" ht="14.5" thickBot="1">
+      <c r="AA3" s="383"/>
+    </row>
+    <row r="4" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="44" t="s">
         <v>118</v>
       </c>
@@ -12284,9 +12295,9 @@
       <c r="Z4" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="AA4" s="390"/>
-    </row>
-    <row r="5" spans="1:27">
+      <c r="AA4" s="383"/>
+    </row>
+    <row r="5" spans="1:27" ht="24" x14ac:dyDescent="0.25">
       <c r="A5" s="51">
         <v>8</v>
       </c>
@@ -12365,7 +12376,7 @@
       </c>
       <c r="AA5" s="157"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="51"/>
       <c r="B6" s="55" t="s">
         <v>127</v>
@@ -12439,7 +12450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="51"/>
       <c r="B7" s="55" t="s">
         <v>129</v>
@@ -12513,7 +12524,7 @@
         <v>3434400</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="51"/>
       <c r="B8" s="55" t="s">
         <v>130</v>
@@ -12587,7 +12598,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" ht="24" x14ac:dyDescent="0.25">
       <c r="A9" s="51">
         <v>10</v>
       </c>
@@ -12666,7 +12677,7 @@
       </c>
       <c r="AA9" s="157"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="51"/>
       <c r="B10" s="55" t="s">
         <v>133</v>
@@ -12740,7 +12751,7 @@
         <v>141280</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="14.5">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="51"/>
       <c r="B11" s="55" t="s">
         <v>134</v>
@@ -12814,7 +12825,7 @@
         <v>536896800</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="14.5">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="51"/>
       <c r="B12" s="55" t="s">
         <v>135</v>
@@ -12888,7 +12899,7 @@
         <v>12067</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="23">
+    <row r="13" spans="1:27" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>12</v>
       </c>
@@ -12967,7 +12978,7 @@
       </c>
       <c r="AA13" s="157"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="51"/>
       <c r="B14" s="55" t="s">
         <v>138</v>
@@ -13041,7 +13052,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="51"/>
       <c r="B15" s="55" t="s">
         <v>139</v>
@@ -13115,7 +13126,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="28">
+    <row r="16" spans="1:27" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A16" s="51">
         <v>13</v>
       </c>
@@ -13194,7 +13205,7 @@
       </c>
       <c r="AA16" s="157"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="51"/>
       <c r="B17" s="55" t="s">
         <v>138</v>
@@ -13268,7 +13279,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="51"/>
       <c r="B18" s="55" t="s">
         <v>139</v>
@@ -13342,7 +13353,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="14.5" thickBot="1">
+    <row r="19" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="57"/>
       <c r="C19" s="58"/>
       <c r="D19" s="58"/>
@@ -13370,7 +13381,7 @@
       <c r="Z19" s="200"/>
       <c r="AA19" s="62"/>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="56"/>
       <c r="B20" s="63" t="s">
         <v>141</v>
@@ -13401,7 +13412,7 @@
       <c r="Z20" s="206"/>
       <c r="AA20" s="64"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="56"/>
       <c r="B21" s="65" t="s">
         <v>142</v>
@@ -13432,7 +13443,7 @@
       <c r="Z21" s="195"/>
       <c r="AA21" s="56"/>
     </row>
-    <row r="22" spans="1:27" ht="14.5" thickBot="1">
+    <row r="22" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="56"/>
       <c r="B22" s="65" t="s">
         <v>143</v>
@@ -13463,7 +13474,7 @@
       <c r="Z22" s="200"/>
       <c r="AA22" s="56"/>
     </row>
-    <row r="23" spans="1:27" ht="28">
+    <row r="23" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="56"/>
       <c r="B23" s="32" t="s">
         <v>144</v>
@@ -13500,7 +13511,7 @@
       <c r="Z23" s="54"/>
       <c r="AA23" s="54"/>
     </row>
-    <row r="24" spans="1:27" s="69" customFormat="1" ht="28">
+    <row r="24" spans="1:27" s="69" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="68"/>
       <c r="B24" s="32" t="s">
         <v>146</v>
@@ -13537,7 +13548,7 @@
       <c r="Z24" s="54"/>
       <c r="AA24" s="54"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="G26"/>
       <c r="H26"/>
       <c r="L26"/>
@@ -13556,7 +13567,7 @@
       <c r="Y26"/>
       <c r="Z26"/>
     </row>
-    <row r="27" spans="1:27" s="73" customFormat="1" ht="28">
+    <row r="27" spans="1:27" s="73" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="70"/>
       <c r="B27" s="35" t="s">
         <v>72</v>
@@ -13633,7 +13644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="56"/>
       <c r="B28" s="74" t="s">
         <v>127</v>
@@ -13680,7 +13691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="56"/>
       <c r="B29" s="74" t="s">
         <v>129</v>
@@ -13751,7 +13762,7 @@
         <v>2142720</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="74" t="s">
         <v>130</v>
@@ -13798,7 +13809,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="G31" s="39">
         <v>1</v>
       </c>
@@ -13863,6 +13874,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="S1:W1"/>
+    <mergeCell ref="X1:Z1"/>
     <mergeCell ref="AA1:AA4"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
@@ -13871,11 +13887,6 @@
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="M1:R1"/>
-    <mergeCell ref="S1:W1"/>
-    <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13884,122 +13895,122 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86FFFA7-3721-4AD9-9178-087228ED3C1F}">
   <dimension ref="A1:AA39"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.25" style="39" customWidth="1"/>
-    <col min="2" max="2" width="38.25" style="92" customWidth="1"/>
-    <col min="3" max="3" width="19.25" style="39" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="39" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" style="92" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="39" customWidth="1"/>
     <col min="4" max="4" width="11" style="39" customWidth="1"/>
-    <col min="5" max="5" width="10.75" style="39" customWidth="1"/>
-    <col min="6" max="6" width="11.4140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" style="39" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.75" style="39" customWidth="1"/>
-    <col min="12" max="12" width="20.4140625" style="39" customWidth="1"/>
-    <col min="13" max="14" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.75" style="39" customWidth="1"/>
-    <col min="16" max="19" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.83203125" style="39" customWidth="1"/>
-    <col min="21" max="21" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.4140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="39" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" style="39" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" style="39" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" style="39" customWidth="1"/>
+    <col min="13" max="14" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.7109375" style="39" customWidth="1"/>
+    <col min="16" max="19" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="39" customWidth="1"/>
+    <col min="21" max="21" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.42578125" style="39" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14" style="39" customWidth="1"/>
-    <col min="28" max="28" width="13.1640625" style="39" customWidth="1"/>
-    <col min="29" max="29" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.1640625" style="39"/>
+    <col min="28" max="28" width="13.140625" style="39" customWidth="1"/>
+    <col min="29" max="29" width="10.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="14.5" thickBot="1"/>
-    <row r="2" spans="1:27" ht="18.5" thickBot="1">
-      <c r="A2" s="384" t="s">
+    <row r="1" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="385" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="385"/>
-      <c r="C2" s="385"/>
-      <c r="D2" s="386"/>
+      <c r="B2" s="386"/>
+      <c r="C2" s="386"/>
+      <c r="D2" s="387"/>
       <c r="F2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="287" t="s">
+      <c r="G2" s="317" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="289"/>
-      <c r="I2" s="289"/>
-      <c r="J2" s="289"/>
-      <c r="K2" s="289"/>
-      <c r="L2" s="289"/>
-      <c r="M2" s="387" t="s">
+      <c r="H2" s="319"/>
+      <c r="I2" s="319"/>
+      <c r="J2" s="319"/>
+      <c r="K2" s="319"/>
+      <c r="L2" s="319"/>
+      <c r="M2" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="N2" s="387"/>
-      <c r="O2" s="387"/>
-      <c r="P2" s="387"/>
-      <c r="Q2" s="387"/>
-      <c r="R2" s="387"/>
-      <c r="S2" s="297" t="s">
+      <c r="N2" s="388"/>
+      <c r="O2" s="388"/>
+      <c r="P2" s="388"/>
+      <c r="Q2" s="388"/>
+      <c r="R2" s="388"/>
+      <c r="S2" s="327" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="297"/>
-      <c r="U2" s="297"/>
-      <c r="V2" s="297"/>
-      <c r="W2" s="297"/>
-      <c r="X2" s="388" t="s">
+      <c r="T2" s="327"/>
+      <c r="U2" s="327"/>
+      <c r="V2" s="327"/>
+      <c r="W2" s="327"/>
+      <c r="X2" s="389" t="s">
         <v>86</v>
       </c>
-      <c r="Y2" s="388"/>
-      <c r="Z2" s="388"/>
-      <c r="AA2" s="392" t="s">
+      <c r="Y2" s="389"/>
+      <c r="Z2" s="389"/>
+      <c r="AA2" s="390" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="14.5" thickBot="1">
+    <row r="3" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F3" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="303" t="s">
+      <c r="G3" s="333" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="305"/>
-      <c r="I3" s="305"/>
-      <c r="J3" s="305" t="s">
+      <c r="H3" s="335"/>
+      <c r="I3" s="335"/>
+      <c r="J3" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="K3" s="305"/>
-      <c r="L3" s="305"/>
-      <c r="M3" s="305" t="s">
+      <c r="K3" s="335"/>
+      <c r="L3" s="335"/>
+      <c r="M3" s="335" t="s">
         <v>91</v>
       </c>
-      <c r="N3" s="305"/>
-      <c r="O3" s="305"/>
-      <c r="P3" s="305" t="s">
+      <c r="N3" s="335"/>
+      <c r="O3" s="335"/>
+      <c r="P3" s="335" t="s">
         <v>92</v>
       </c>
-      <c r="Q3" s="305"/>
-      <c r="R3" s="305"/>
-      <c r="S3" s="305" t="s">
+      <c r="Q3" s="335"/>
+      <c r="R3" s="335"/>
+      <c r="S3" s="335" t="s">
         <v>93</v>
       </c>
-      <c r="T3" s="305"/>
-      <c r="U3" s="305" t="s">
+      <c r="T3" s="335"/>
+      <c r="U3" s="335" t="s">
         <v>94</v>
       </c>
-      <c r="V3" s="305"/>
-      <c r="W3" s="305"/>
+      <c r="V3" s="335"/>
+      <c r="W3" s="335"/>
       <c r="X3" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="Y3" s="391" t="s">
+      <c r="Y3" s="384" t="s">
         <v>96</v>
       </c>
-      <c r="Z3" s="391"/>
-      <c r="AA3" s="393"/>
-    </row>
-    <row r="4" spans="1:27" ht="14.5" thickBot="1">
+      <c r="Z3" s="384"/>
+      <c r="AA3" s="391"/>
+    </row>
+    <row r="4" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F4" s="41" t="s">
         <v>97</v>
       </c>
@@ -14063,9 +14074,9 @@
       <c r="Z4" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="AA4" s="393"/>
-    </row>
-    <row r="5" spans="1:27" ht="14.5" thickBot="1">
+      <c r="AA4" s="391"/>
+    </row>
+    <row r="5" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="138" t="s">
         <v>118</v>
       </c>
@@ -14144,9 +14155,9 @@
       <c r="Z5" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AA5" s="393"/>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="AA5" s="391"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="142"/>
       <c r="B6" s="143" t="s">
         <v>211</v>
@@ -14177,7 +14188,7 @@
       <c r="Z6" s="148"/>
       <c r="AA6" s="149"/>
     </row>
-    <row r="7" spans="1:27" ht="28">
+    <row r="7" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="51">
         <v>1</v>
       </c>
@@ -14256,7 +14267,7 @@
       </c>
       <c r="AA7" s="87"/>
     </row>
-    <row r="8" spans="1:27" ht="28">
+    <row r="8" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>2</v>
       </c>
@@ -14335,7 +14346,7 @@
       </c>
       <c r="AA8" s="87"/>
     </row>
-    <row r="9" spans="1:27" ht="28">
+    <row r="9" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="51">
         <v>3</v>
       </c>
@@ -14414,7 +14425,7 @@
       </c>
       <c r="AA9" s="87"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="51"/>
       <c r="B10" s="150"/>
       <c r="C10" s="52"/>
@@ -14443,7 +14454,7 @@
       <c r="Z10" s="88"/>
       <c r="AA10" s="87"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="51"/>
       <c r="B11" s="150"/>
       <c r="C11" s="52"/>
@@ -14472,7 +14483,7 @@
       <c r="Z11" s="88"/>
       <c r="AA11" s="87"/>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="51"/>
       <c r="B12" s="150"/>
       <c r="C12" s="52"/>
@@ -14501,7 +14512,7 @@
       <c r="Z12" s="153"/>
       <c r="AA12" s="87"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="51"/>
       <c r="B13" s="154"/>
       <c r="C13" s="52"/>
@@ -14530,7 +14541,7 @@
       <c r="Z13" s="83"/>
       <c r="AA13" s="156"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="51"/>
       <c r="B14" s="150"/>
       <c r="C14" s="52"/>
@@ -14559,7 +14570,7 @@
       <c r="Z14" s="89"/>
       <c r="AA14" s="88"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="51"/>
       <c r="B15" s="150"/>
       <c r="C15" s="52"/>
@@ -14588,7 +14599,7 @@
       <c r="Z15" s="87"/>
       <c r="AA15" s="88"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="51"/>
       <c r="B16" s="150"/>
       <c r="C16" s="52"/>
@@ -14617,7 +14628,7 @@
       <c r="Z16" s="89"/>
       <c r="AA16" s="88"/>
     </row>
-    <row r="19" spans="3:11">
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C19" s="169" t="s">
         <v>220</v>
       </c>
@@ -14626,7 +14637,7 @@
       </c>
       <c r="G19" s="91"/>
     </row>
-    <row r="20" spans="3:11">
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C20" s="169" t="s">
         <v>221</v>
       </c>
@@ -14636,7 +14647,7 @@
       <c r="J20" s="93"/>
       <c r="K20" s="93"/>
     </row>
-    <row r="21" spans="3:11">
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C21" s="169" t="s">
         <v>222</v>
       </c>
@@ -14644,7 +14655,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="3:11">
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C22" s="169" t="s">
         <v>223</v>
       </c>
@@ -14652,7 +14663,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="3:11">
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C23" s="169" t="s">
         <v>224</v>
       </c>
@@ -14660,7 +14671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="3:11">
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C24" s="169" t="s">
         <v>225</v>
       </c>
@@ -14668,7 +14679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="3:11">
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C25" s="169" t="s">
         <v>226</v>
       </c>
@@ -14677,7 +14688,7 @@
       </c>
       <c r="E25" s="92"/>
     </row>
-    <row r="26" spans="3:11">
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C26" s="169" t="s">
         <v>227</v>
       </c>
@@ -14685,7 +14696,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="3:11">
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C27" s="169" t="s">
         <v>228</v>
       </c>
@@ -14693,7 +14704,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="3:11">
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C28" s="169" t="s">
         <v>229</v>
       </c>
@@ -14701,7 +14712,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="3:11">
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C29" s="169" t="s">
         <v>230</v>
       </c>
@@ -14709,7 +14720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="3:11">
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C30" s="169" t="s">
         <v>231</v>
       </c>
@@ -14717,7 +14728,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="3:11">
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C31" s="169" t="s">
         <v>232</v>
       </c>
@@ -14725,7 +14736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="3:11">
+    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C32" s="169" t="s">
         <v>233</v>
       </c>
@@ -14733,7 +14744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="3:4">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C33" s="169" t="s">
         <v>234</v>
       </c>
@@ -14741,7 +14752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="3:4">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C34" s="169" t="s">
         <v>235</v>
       </c>
@@ -14749,7 +14760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="3:4">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C35" s="169" t="s">
         <v>236</v>
       </c>
@@ -14757,7 +14768,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="3:4">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C36" s="169" t="s">
         <v>237</v>
       </c>
@@ -14765,7 +14776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="3:4">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C37" s="169" t="s">
         <v>238</v>
       </c>
@@ -14773,7 +14784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="3:4">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C38" s="169" t="s">
         <v>239</v>
       </c>
@@ -14781,7 +14792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="3:4">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
       <c r="D39" s="39">
         <f>SUM(D19:D38)</f>
         <v>275</v>
@@ -14789,6 +14800,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="S2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AA2:AA5"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:L3"/>
@@ -14797,11 +14813,6 @@
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="G2:L2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="S2:W2"/>
-    <mergeCell ref="X2:Z2"/>
   </mergeCells>
   <conditionalFormatting sqref="C19:C38">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -14813,122 +14824,122 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F13EC25-7C33-4B88-84BE-0590ADD417AF}">
   <dimension ref="A1:AA26"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.25" style="39" customWidth="1"/>
-    <col min="2" max="2" width="36.75" style="39" customWidth="1"/>
-    <col min="3" max="3" width="19.25" style="39" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="39" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" style="39" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="39" customWidth="1"/>
     <col min="4" max="4" width="11" style="39" customWidth="1"/>
-    <col min="5" max="5" width="10.75" style="39" customWidth="1"/>
-    <col min="6" max="6" width="11.4140625" style="39" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" style="39" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.75" style="39" customWidth="1"/>
-    <col min="12" max="12" width="20.4140625" style="39" customWidth="1"/>
-    <col min="13" max="14" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.75" style="39" customWidth="1"/>
-    <col min="16" max="19" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.83203125" style="39" customWidth="1"/>
-    <col min="21" max="21" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.83203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.1640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="39" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" style="39" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" style="39" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" style="39" customWidth="1"/>
+    <col min="13" max="14" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.7109375" style="39" customWidth="1"/>
+    <col min="16" max="19" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="39" customWidth="1"/>
+    <col min="21" max="21" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.140625" style="39" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14" style="39" customWidth="1"/>
-    <col min="28" max="28" width="13.1640625" style="39" customWidth="1"/>
-    <col min="29" max="29" width="10.1640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.1640625" style="39"/>
+    <col min="28" max="28" width="13.140625" style="39" customWidth="1"/>
+    <col min="29" max="29" width="10.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="14.5" thickBot="1"/>
-    <row r="2" spans="1:27" ht="18.5" thickBot="1">
-      <c r="A2" s="384" t="s">
+    <row r="1" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="385" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="385"/>
-      <c r="C2" s="385"/>
-      <c r="D2" s="386"/>
+      <c r="B2" s="386"/>
+      <c r="C2" s="386"/>
+      <c r="D2" s="387"/>
       <c r="F2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="287" t="s">
+      <c r="G2" s="317" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="289"/>
-      <c r="I2" s="289"/>
-      <c r="J2" s="289"/>
-      <c r="K2" s="289"/>
-      <c r="L2" s="289"/>
-      <c r="M2" s="387" t="s">
+      <c r="H2" s="319"/>
+      <c r="I2" s="319"/>
+      <c r="J2" s="319"/>
+      <c r="K2" s="319"/>
+      <c r="L2" s="319"/>
+      <c r="M2" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="N2" s="387"/>
-      <c r="O2" s="387"/>
-      <c r="P2" s="387"/>
-      <c r="Q2" s="387"/>
-      <c r="R2" s="387"/>
-      <c r="S2" s="297" t="s">
+      <c r="N2" s="388"/>
+      <c r="O2" s="388"/>
+      <c r="P2" s="388"/>
+      <c r="Q2" s="388"/>
+      <c r="R2" s="388"/>
+      <c r="S2" s="327" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="297"/>
-      <c r="U2" s="297"/>
-      <c r="V2" s="297"/>
-      <c r="W2" s="297"/>
-      <c r="X2" s="388" t="s">
+      <c r="T2" s="327"/>
+      <c r="U2" s="327"/>
+      <c r="V2" s="327"/>
+      <c r="W2" s="327"/>
+      <c r="X2" s="389" t="s">
         <v>86</v>
       </c>
-      <c r="Y2" s="388"/>
-      <c r="Z2" s="388"/>
-      <c r="AA2" s="392" t="s">
+      <c r="Y2" s="389"/>
+      <c r="Z2" s="389"/>
+      <c r="AA2" s="390" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="14.5" thickBot="1">
+    <row r="3" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F3" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="303" t="s">
+      <c r="G3" s="333" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="305"/>
-      <c r="I3" s="305"/>
-      <c r="J3" s="305" t="s">
+      <c r="H3" s="335"/>
+      <c r="I3" s="335"/>
+      <c r="J3" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="K3" s="305"/>
-      <c r="L3" s="305"/>
-      <c r="M3" s="305" t="s">
+      <c r="K3" s="335"/>
+      <c r="L3" s="335"/>
+      <c r="M3" s="335" t="s">
         <v>91</v>
       </c>
-      <c r="N3" s="305"/>
-      <c r="O3" s="305"/>
-      <c r="P3" s="305" t="s">
+      <c r="N3" s="335"/>
+      <c r="O3" s="335"/>
+      <c r="P3" s="335" t="s">
         <v>92</v>
       </c>
-      <c r="Q3" s="305"/>
-      <c r="R3" s="305"/>
-      <c r="S3" s="305" t="s">
+      <c r="Q3" s="335"/>
+      <c r="R3" s="335"/>
+      <c r="S3" s="335" t="s">
         <v>93</v>
       </c>
-      <c r="T3" s="305"/>
-      <c r="U3" s="305" t="s">
+      <c r="T3" s="335"/>
+      <c r="U3" s="335" t="s">
         <v>94</v>
       </c>
-      <c r="V3" s="305"/>
-      <c r="W3" s="305"/>
+      <c r="V3" s="335"/>
+      <c r="W3" s="335"/>
       <c r="X3" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="Y3" s="391" t="s">
+      <c r="Y3" s="384" t="s">
         <v>96</v>
       </c>
-      <c r="Z3" s="391"/>
-      <c r="AA3" s="393"/>
-    </row>
-    <row r="4" spans="1:27" ht="14.5" thickBot="1">
+      <c r="Z3" s="384"/>
+      <c r="AA3" s="391"/>
+    </row>
+    <row r="4" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F4" s="41" t="s">
         <v>97</v>
       </c>
@@ -14992,9 +15003,9 @@
       <c r="Z4" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="AA4" s="393"/>
-    </row>
-    <row r="5" spans="1:27" ht="14.5" thickBot="1">
+      <c r="AA4" s="391"/>
+    </row>
+    <row r="5" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>118</v>
       </c>
@@ -15073,9 +15084,9 @@
       <c r="Z5" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AA5" s="393"/>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="AA5" s="391"/>
+    </row>
+    <row r="6" spans="1:27" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="51">
         <v>8</v>
       </c>
@@ -15156,7 +15167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="51"/>
       <c r="B7" s="78" t="s">
         <v>127</v>
@@ -15225,7 +15236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="51"/>
       <c r="B8" s="78" t="s">
         <v>129</v>
@@ -15298,7 +15309,7 @@
         <v>241920</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="51"/>
       <c r="B9" s="78" t="s">
         <v>130</v>
@@ -15371,7 +15382,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="51">
         <v>9</v>
       </c>
@@ -15452,7 +15463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="51"/>
       <c r="B11" s="81" t="s">
         <v>127</v>
@@ -15525,7 +15536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="51"/>
       <c r="B12" s="81" t="s">
         <v>132</v>
@@ -15598,7 +15609,7 @@
         <v>645120</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="51"/>
       <c r="B13" s="81" t="s">
         <v>130</v>
@@ -15671,7 +15682,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="51">
         <v>10</v>
       </c>
@@ -15752,7 +15763,7 @@
         <v>0.99998732157664061</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="51"/>
       <c r="B15" s="55" t="s">
         <v>127</v>
@@ -15799,7 +15810,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="51"/>
       <c r="B16" s="55" t="s">
         <v>132</v>
@@ -15872,7 +15883,7 @@
         <v>21611520</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="51"/>
       <c r="B17" s="55" t="s">
         <v>130</v>
@@ -15945,10 +15956,10 @@
         <v>536</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="G20" s="91"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B21" s="92"/>
       <c r="J21" s="93" t="s">
         <v>151</v>
@@ -15957,15 +15968,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B22" s="92"/>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B26" s="92"/>
       <c r="E26" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="S2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AA2:AA5"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:L3"/>
@@ -15974,11 +15990,6 @@
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="G2:L2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="S2:W2"/>
-    <mergeCell ref="X2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15987,74 +15998,74 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59EAB9BD-9D0A-43AB-90A3-5EDE0BBBDABE}">
   <dimension ref="A1:AA11"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="19.75" customWidth="1"/>
-    <col min="5" max="5" width="12.58203125" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.4140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.4140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="18.5" thickBot="1">
-      <c r="A1" s="384" t="s">
+    <row r="1" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="385" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="385"/>
-      <c r="C1" s="385"/>
-      <c r="D1" s="386"/>
+      <c r="B1" s="386"/>
+      <c r="C1" s="386"/>
+      <c r="D1" s="387"/>
       <c r="E1" s="39"/>
       <c r="F1" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="287" t="s">
+      <c r="G1" s="317" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="289"/>
-      <c r="I1" s="289"/>
-      <c r="J1" s="289"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="289"/>
-      <c r="M1" s="387" t="s">
+      <c r="H1" s="319"/>
+      <c r="I1" s="319"/>
+      <c r="J1" s="319"/>
+      <c r="K1" s="319"/>
+      <c r="L1" s="319"/>
+      <c r="M1" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="N1" s="387"/>
-      <c r="O1" s="387"/>
-      <c r="P1" s="387"/>
-      <c r="Q1" s="387"/>
-      <c r="R1" s="387"/>
-      <c r="S1" s="297" t="s">
+      <c r="N1" s="388"/>
+      <c r="O1" s="388"/>
+      <c r="P1" s="388"/>
+      <c r="Q1" s="388"/>
+      <c r="R1" s="388"/>
+      <c r="S1" s="327" t="s">
         <v>85</v>
       </c>
-      <c r="T1" s="297"/>
-      <c r="U1" s="297"/>
-      <c r="V1" s="297"/>
-      <c r="W1" s="297"/>
-      <c r="X1" s="388" t="s">
+      <c r="T1" s="327"/>
+      <c r="U1" s="327"/>
+      <c r="V1" s="327"/>
+      <c r="W1" s="327"/>
+      <c r="X1" s="389" t="s">
         <v>86</v>
       </c>
-      <c r="Y1" s="388"/>
-      <c r="Z1" s="388"/>
-      <c r="AA1" s="392" t="s">
+      <c r="Y1" s="389"/>
+      <c r="Z1" s="389"/>
+      <c r="AA1" s="390" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="14.5" thickBot="1">
+    <row r="2" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="39"/>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -16063,45 +16074,45 @@
       <c r="F2" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="303" t="s">
+      <c r="G2" s="333" t="s">
         <v>89</v>
       </c>
-      <c r="H2" s="305"/>
-      <c r="I2" s="305"/>
-      <c r="J2" s="305" t="s">
+      <c r="H2" s="335"/>
+      <c r="I2" s="335"/>
+      <c r="J2" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="K2" s="305"/>
-      <c r="L2" s="305"/>
-      <c r="M2" s="305" t="s">
+      <c r="K2" s="335"/>
+      <c r="L2" s="335"/>
+      <c r="M2" s="335" t="s">
         <v>91</v>
       </c>
-      <c r="N2" s="305"/>
-      <c r="O2" s="305"/>
-      <c r="P2" s="305" t="s">
+      <c r="N2" s="335"/>
+      <c r="O2" s="335"/>
+      <c r="P2" s="335" t="s">
         <v>92</v>
       </c>
-      <c r="Q2" s="305"/>
-      <c r="R2" s="305"/>
-      <c r="S2" s="305" t="s">
+      <c r="Q2" s="335"/>
+      <c r="R2" s="335"/>
+      <c r="S2" s="335" t="s">
         <v>93</v>
       </c>
-      <c r="T2" s="305"/>
-      <c r="U2" s="305" t="s">
+      <c r="T2" s="335"/>
+      <c r="U2" s="335" t="s">
         <v>94</v>
       </c>
-      <c r="V2" s="305"/>
-      <c r="W2" s="305"/>
+      <c r="V2" s="335"/>
+      <c r="W2" s="335"/>
       <c r="X2" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="Y2" s="391" t="s">
+      <c r="Y2" s="384" t="s">
         <v>96</v>
       </c>
-      <c r="Z2" s="391"/>
-      <c r="AA2" s="393"/>
-    </row>
-    <row r="3" spans="1:27" ht="14.5" thickBot="1">
+      <c r="Z2" s="384"/>
+      <c r="AA2" s="391"/>
+    </row>
+    <row r="3" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39"/>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -16170,9 +16181,9 @@
       <c r="Z3" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="AA3" s="393"/>
-    </row>
-    <row r="4" spans="1:27" ht="14.5" thickBot="1">
+      <c r="AA3" s="391"/>
+    </row>
+    <row r="4" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="44" t="s">
         <v>118</v>
       </c>
@@ -16251,9 +16262,9 @@
       <c r="Z4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AA4" s="393"/>
-    </row>
-    <row r="5" spans="1:27">
+      <c r="AA4" s="391"/>
+    </row>
+    <row r="5" spans="1:27" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A5" s="51">
         <v>10</v>
       </c>
@@ -16270,69 +16281,69 @@
         <v>77</v>
       </c>
       <c r="F5" s="53"/>
-      <c r="G5" s="280">
+      <c r="G5" s="409">
         <v>0.99950000000000006</v>
       </c>
-      <c r="H5" s="281">
+      <c r="H5" s="410">
         <v>0.99960000000000004</v>
       </c>
-      <c r="I5" s="281">
+      <c r="I5" s="410">
         <v>0.99970000000000003</v>
       </c>
-      <c r="J5" s="280">
+      <c r="J5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="K5" s="280">
+      <c r="K5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="L5" s="280">
+      <c r="L5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="M5" s="280">
+      <c r="M5" s="409">
         <v>0.99950000000000006</v>
       </c>
-      <c r="N5" s="280">
+      <c r="N5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="O5" s="280">
+      <c r="O5" s="409">
         <v>0.99970000000000003</v>
       </c>
-      <c r="P5" s="280">
+      <c r="P5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="Q5" s="280">
+      <c r="Q5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="R5" s="280">
+      <c r="R5" s="409">
         <v>0.99950000000000006</v>
       </c>
-      <c r="S5" s="280">
+      <c r="S5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="T5" s="280">
+      <c r="T5" s="409">
         <v>0.99970000000000003</v>
       </c>
-      <c r="U5" s="280">
+      <c r="U5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="V5" s="280">
+      <c r="V5" s="409">
         <v>0.99950000000000006</v>
       </c>
-      <c r="W5" s="280">
+      <c r="W5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="X5" s="280">
+      <c r="X5" s="409">
         <v>0.99960000000000004</v>
       </c>
-      <c r="Y5" s="280">
+      <c r="Y5" s="409">
         <v>0.99970000000000003</v>
       </c>
-      <c r="Z5" s="280">
+      <c r="Z5" s="409">
         <v>0.99960000000000004</v>
       </c>
       <c r="AA5" s="56"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="51"/>
       <c r="B6" s="55" t="s">
         <v>258</v>
@@ -16363,7 +16374,7 @@
       <c r="Z6" s="184"/>
       <c r="AA6" s="56"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="51"/>
       <c r="B7" s="55" t="s">
         <v>259</v>
@@ -16394,7 +16405,7 @@
       <c r="Z7" s="184"/>
       <c r="AA7" s="56"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>11</v>
       </c>
@@ -16433,7 +16444,7 @@
       <c r="Z8" s="182"/>
       <c r="AA8" s="56"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="185"/>
       <c r="B9" s="55" t="s">
         <v>258</v>
@@ -16464,7 +16475,7 @@
       <c r="Z9" s="184"/>
       <c r="AA9" s="56"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="185"/>
       <c r="B10" s="55" t="s">
         <v>261</v>
@@ -16495,7 +16506,7 @@
       <c r="Z10" s="184"/>
       <c r="AA10" s="56"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="187" t="s">
         <v>262</v>
@@ -16573,6 +16584,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="S1:W1"/>
+    <mergeCell ref="X1:Z1"/>
     <mergeCell ref="AA1:AA4"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
@@ -16581,11 +16597,6 @@
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="M1:R1"/>
-    <mergeCell ref="S1:W1"/>
-    <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16594,103 +16605,103 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58375844-D0BB-49A1-AB78-55507912F8D2}">
   <dimension ref="A1:AD18"/>
-  <sheetFormatPr defaultColWidth="23" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="23" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.4140625" style="95" customWidth="1"/>
-    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" style="95" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="29.58203125" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" style="94" customWidth="1"/>
-    <col min="7" max="7" width="16.75" style="39" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" style="94" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" style="39" customWidth="1"/>
     <col min="8" max="9" width="23" style="39"/>
-    <col min="10" max="29" width="16.25" customWidth="1"/>
-    <col min="30" max="30" width="18.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="29" width="16.28515625" customWidth="1"/>
+    <col min="30" max="30" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="18.5" thickBot="1">
-      <c r="A1" s="384" t="s">
+    <row r="1" spans="1:30" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="385" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="385"/>
-      <c r="C1" s="385"/>
-      <c r="D1" s="386"/>
-    </row>
-    <row r="4" spans="1:30" ht="14.5" thickBot="1"/>
-    <row r="5" spans="1:30" ht="14.5" thickBot="1">
+      <c r="B1" s="386"/>
+      <c r="C1" s="386"/>
+      <c r="D1" s="387"/>
+    </row>
+    <row r="4" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J5" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="K5" s="287" t="s">
+      <c r="K5" s="317" t="s">
         <v>83</v>
       </c>
-      <c r="L5" s="289"/>
-      <c r="M5" s="289"/>
-      <c r="N5" s="289"/>
-      <c r="O5" s="289"/>
-      <c r="P5" s="289"/>
-      <c r="Q5" s="387" t="s">
+      <c r="L5" s="319"/>
+      <c r="M5" s="319"/>
+      <c r="N5" s="319"/>
+      <c r="O5" s="319"/>
+      <c r="P5" s="319"/>
+      <c r="Q5" s="388" t="s">
         <v>84</v>
       </c>
-      <c r="R5" s="387"/>
-      <c r="S5" s="387"/>
-      <c r="T5" s="387"/>
-      <c r="U5" s="387"/>
-      <c r="V5" s="387"/>
-      <c r="W5" s="297" t="s">
+      <c r="R5" s="388"/>
+      <c r="S5" s="388"/>
+      <c r="T5" s="388"/>
+      <c r="U5" s="388"/>
+      <c r="V5" s="388"/>
+      <c r="W5" s="327" t="s">
         <v>85</v>
       </c>
-      <c r="X5" s="297"/>
-      <c r="Y5" s="297"/>
-      <c r="Z5" s="297"/>
-      <c r="AA5" s="297"/>
-      <c r="AB5" s="388" t="s">
+      <c r="X5" s="327"/>
+      <c r="Y5" s="327"/>
+      <c r="Z5" s="327"/>
+      <c r="AA5" s="327"/>
+      <c r="AB5" s="389" t="s">
         <v>86</v>
       </c>
-      <c r="AC5" s="388"/>
-      <c r="AD5" s="388"/>
-    </row>
-    <row r="6" spans="1:30" ht="14.5" thickBot="1">
+      <c r="AC5" s="389"/>
+      <c r="AD5" s="389"/>
+    </row>
+    <row r="6" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J6" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="K6" s="395" t="s">
+      <c r="K6" s="393" t="s">
         <v>89</v>
       </c>
-      <c r="L6" s="396"/>
-      <c r="M6" s="305"/>
-      <c r="N6" s="305" t="s">
+      <c r="L6" s="394"/>
+      <c r="M6" s="335"/>
+      <c r="N6" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="O6" s="305"/>
-      <c r="P6" s="305"/>
-      <c r="Q6" s="305" t="s">
+      <c r="O6" s="335"/>
+      <c r="P6" s="335"/>
+      <c r="Q6" s="335" t="s">
         <v>91</v>
       </c>
-      <c r="R6" s="305"/>
-      <c r="S6" s="305"/>
-      <c r="T6" s="305" t="s">
+      <c r="R6" s="335"/>
+      <c r="S6" s="335"/>
+      <c r="T6" s="335" t="s">
         <v>92</v>
       </c>
-      <c r="U6" s="305"/>
-      <c r="V6" s="305"/>
-      <c r="W6" s="305" t="s">
+      <c r="U6" s="335"/>
+      <c r="V6" s="335"/>
+      <c r="W6" s="335" t="s">
         <v>93</v>
       </c>
-      <c r="X6" s="305"/>
-      <c r="Y6" s="305" t="s">
+      <c r="X6" s="335"/>
+      <c r="Y6" s="335" t="s">
         <v>94</v>
       </c>
-      <c r="Z6" s="305"/>
-      <c r="AA6" s="305"/>
+      <c r="Z6" s="335"/>
+      <c r="AA6" s="335"/>
       <c r="AB6" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="AC6" s="391" t="s">
+      <c r="AC6" s="384" t="s">
         <v>96</v>
       </c>
-      <c r="AD6" s="391"/>
-    </row>
-    <row r="7" spans="1:30">
+      <c r="AD6" s="384"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="J7" s="40" t="s">
         <v>97</v>
       </c>
@@ -16755,7 +16766,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="14.5" thickBot="1">
+    <row r="8" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J8" s="97" t="s">
         <v>123</v>
       </c>
@@ -16820,7 +16831,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="36">
+    <row r="9" spans="1:30" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A9" s="98" t="s">
         <v>118</v>
       </c>
@@ -16870,7 +16881,7 @@
       <c r="AC9" s="101"/>
       <c r="AD9" s="102"/>
     </row>
-    <row r="10" spans="1:30" s="107" customFormat="1" ht="56">
+    <row r="10" spans="1:30" s="107" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="70">
         <v>1</v>
       </c>
@@ -16960,7 +16971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="107" customFormat="1" ht="84">
+    <row r="11" spans="1:30" s="107" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="70">
         <v>2</v>
       </c>
@@ -17050,7 +17061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:30" s="107" customFormat="1" ht="28">
+    <row r="12" spans="1:30" s="107" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="70">
         <v>3</v>
       </c>
@@ -17140,7 +17151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:30" s="107" customFormat="1" ht="42">
+    <row r="13" spans="1:30" s="107" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="70">
         <v>4</v>
       </c>
@@ -17230,7 +17241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:30" s="107" customFormat="1" ht="56">
+    <row r="14" spans="1:30" s="107" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="70">
         <v>5</v>
       </c>
@@ -17320,7 +17331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:30" s="107" customFormat="1" ht="56">
+    <row r="15" spans="1:30" s="107" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="70">
         <v>6</v>
       </c>
@@ -17410,7 +17421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:30" s="107" customFormat="1" ht="28">
+    <row r="16" spans="1:30" s="107" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="70">
         <v>7</v>
       </c>
@@ -17500,7 +17511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:30" s="107" customFormat="1" ht="28">
+    <row r="17" spans="1:30" s="107" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="70">
         <v>8</v>
       </c>
@@ -17590,19 +17601,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:30">
-      <c r="A18" s="394" t="s">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A18" s="392" t="s">
         <v>284</v>
       </c>
-      <c r="B18" s="394"/>
-      <c r="C18" s="394"/>
-      <c r="D18" s="394"/>
-      <c r="E18" s="394"/>
-      <c r="F18" s="394"/>
-      <c r="G18" s="394"/>
-      <c r="H18" s="394"/>
-      <c r="I18" s="394"/>
-      <c r="J18" s="394"/>
+      <c r="B18" s="392"/>
+      <c r="C18" s="392"/>
+      <c r="D18" s="392"/>
+      <c r="E18" s="392"/>
+      <c r="F18" s="392"/>
+      <c r="G18" s="392"/>
+      <c r="H18" s="392"/>
+      <c r="I18" s="392"/>
+      <c r="J18" s="392"/>
       <c r="K18" s="192">
         <f>K10*0.1+K11*0.2+K12*0.2+K13*0.1+K14*0.1+K15*0.2+K16*0.05+K17*0.05</f>
         <v>1</v>
@@ -17707,256 +17718,256 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECEFE1AC-6E8D-49BE-91DC-39122B36F5CD}">
   <dimension ref="A1:AY55"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.58203125" style="108" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.58203125" style="108" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" style="108" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5703125" style="108" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="108" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.25" style="108" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="108" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.4140625" style="108" customWidth="1"/>
-    <col min="7" max="7" width="16.4140625" style="108" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" style="108" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="108" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="108" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" style="108" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="108" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="40.25" style="108" customWidth="1"/>
-    <col min="10" max="22" width="9.58203125" style="109" customWidth="1"/>
-    <col min="23" max="23" width="9.58203125" style="110" customWidth="1"/>
-    <col min="24" max="27" width="9.58203125" style="109" customWidth="1"/>
-    <col min="28" max="28" width="9.83203125" style="109" customWidth="1"/>
-    <col min="29" max="33" width="9.58203125" style="109" customWidth="1"/>
+    <col min="9" max="9" width="40.28515625" style="108" customWidth="1"/>
+    <col min="10" max="22" width="9.5703125" style="109" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" style="110" customWidth="1"/>
+    <col min="24" max="27" width="9.5703125" style="109" customWidth="1"/>
+    <col min="28" max="28" width="9.85546875" style="109" customWidth="1"/>
+    <col min="29" max="33" width="9.5703125" style="109" customWidth="1"/>
     <col min="34" max="34" width="10" style="109" customWidth="1"/>
-    <col min="35" max="48" width="9.58203125" style="109" customWidth="1"/>
-    <col min="49" max="49" width="16.1640625" style="109" bestFit="1" customWidth="1"/>
-    <col min="50" max="16384" width="9.1640625" style="108"/>
+    <col min="35" max="48" width="9.5703125" style="109" customWidth="1"/>
+    <col min="49" max="49" width="16.140625" style="109" bestFit="1" customWidth="1"/>
+    <col min="50" max="16384" width="9.140625" style="108"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="13" thickBot="1"/>
-    <row r="2" spans="1:51" ht="15.75" customHeight="1" thickBot="1">
+    <row r="1" spans="1:51" ht="14.25" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I2" s="111" t="s">
         <v>82</v>
       </c>
-      <c r="J2" s="287" t="s">
+      <c r="J2" s="317" t="s">
         <v>83</v>
       </c>
-      <c r="K2" s="289"/>
-      <c r="L2" s="289"/>
-      <c r="M2" s="289"/>
-      <c r="N2" s="289"/>
-      <c r="O2" s="289"/>
-      <c r="P2" s="289"/>
-      <c r="Q2" s="289"/>
-      <c r="R2" s="289"/>
-      <c r="S2" s="289"/>
-      <c r="T2" s="289"/>
-      <c r="U2" s="291"/>
-      <c r="V2" s="408" t="s">
+      <c r="K2" s="319"/>
+      <c r="L2" s="319"/>
+      <c r="M2" s="319"/>
+      <c r="N2" s="319"/>
+      <c r="O2" s="319"/>
+      <c r="P2" s="319"/>
+      <c r="Q2" s="319"/>
+      <c r="R2" s="319"/>
+      <c r="S2" s="319"/>
+      <c r="T2" s="319"/>
+      <c r="U2" s="321"/>
+      <c r="V2" s="397" t="s">
         <v>84</v>
       </c>
-      <c r="W2" s="387"/>
-      <c r="X2" s="387"/>
-      <c r="Y2" s="387"/>
-      <c r="Z2" s="387"/>
-      <c r="AA2" s="387"/>
-      <c r="AB2" s="387"/>
-      <c r="AC2" s="387"/>
-      <c r="AD2" s="387"/>
-      <c r="AE2" s="387"/>
-      <c r="AF2" s="387"/>
-      <c r="AG2" s="387"/>
-      <c r="AH2" s="297" t="s">
+      <c r="W2" s="388"/>
+      <c r="X2" s="388"/>
+      <c r="Y2" s="388"/>
+      <c r="Z2" s="388"/>
+      <c r="AA2" s="388"/>
+      <c r="AB2" s="388"/>
+      <c r="AC2" s="388"/>
+      <c r="AD2" s="388"/>
+      <c r="AE2" s="388"/>
+      <c r="AF2" s="388"/>
+      <c r="AG2" s="388"/>
+      <c r="AH2" s="327" t="s">
         <v>85</v>
       </c>
-      <c r="AI2" s="297"/>
-      <c r="AJ2" s="297"/>
-      <c r="AK2" s="297"/>
-      <c r="AL2" s="297"/>
-      <c r="AM2" s="297"/>
-      <c r="AN2" s="297"/>
-      <c r="AO2" s="297"/>
-      <c r="AP2" s="297"/>
-      <c r="AQ2" s="297"/>
-      <c r="AR2" s="388" t="s">
+      <c r="AI2" s="327"/>
+      <c r="AJ2" s="327"/>
+      <c r="AK2" s="327"/>
+      <c r="AL2" s="327"/>
+      <c r="AM2" s="327"/>
+      <c r="AN2" s="327"/>
+      <c r="AO2" s="327"/>
+      <c r="AP2" s="327"/>
+      <c r="AQ2" s="327"/>
+      <c r="AR2" s="389" t="s">
         <v>86</v>
       </c>
-      <c r="AS2" s="388"/>
-      <c r="AT2" s="388"/>
-      <c r="AU2" s="388"/>
-      <c r="AV2" s="388"/>
-      <c r="AW2" s="406"/>
-    </row>
-    <row r="3" spans="1:51" ht="13.5" thickBot="1">
+      <c r="AS2" s="389"/>
+      <c r="AT2" s="389"/>
+      <c r="AU2" s="389"/>
+      <c r="AV2" s="389"/>
+      <c r="AW2" s="398"/>
+    </row>
+    <row r="3" spans="1:51" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I3" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="303" t="s">
+      <c r="J3" s="333" t="s">
         <v>89</v>
       </c>
-      <c r="K3" s="305"/>
-      <c r="L3" s="305"/>
-      <c r="M3" s="305"/>
-      <c r="N3" s="305"/>
-      <c r="O3" s="305"/>
-      <c r="P3" s="305" t="s">
+      <c r="K3" s="335"/>
+      <c r="L3" s="335"/>
+      <c r="M3" s="335"/>
+      <c r="N3" s="335"/>
+      <c r="O3" s="335"/>
+      <c r="P3" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="Q3" s="305"/>
-      <c r="R3" s="305"/>
-      <c r="S3" s="305"/>
-      <c r="T3" s="305"/>
-      <c r="U3" s="305"/>
-      <c r="V3" s="305" t="s">
+      <c r="Q3" s="335"/>
+      <c r="R3" s="335"/>
+      <c r="S3" s="335"/>
+      <c r="T3" s="335"/>
+      <c r="U3" s="335"/>
+      <c r="V3" s="335" t="s">
         <v>91</v>
       </c>
-      <c r="W3" s="305"/>
-      <c r="X3" s="305"/>
-      <c r="Y3" s="305"/>
-      <c r="Z3" s="305"/>
-      <c r="AA3" s="305"/>
-      <c r="AB3" s="305" t="s">
+      <c r="W3" s="335"/>
+      <c r="X3" s="335"/>
+      <c r="Y3" s="335"/>
+      <c r="Z3" s="335"/>
+      <c r="AA3" s="335"/>
+      <c r="AB3" s="335" t="s">
         <v>92</v>
       </c>
-      <c r="AC3" s="305"/>
-      <c r="AD3" s="305"/>
-      <c r="AE3" s="305"/>
-      <c r="AF3" s="305"/>
-      <c r="AG3" s="305"/>
-      <c r="AH3" s="305" t="s">
+      <c r="AC3" s="335"/>
+      <c r="AD3" s="335"/>
+      <c r="AE3" s="335"/>
+      <c r="AF3" s="335"/>
+      <c r="AG3" s="335"/>
+      <c r="AH3" s="335" t="s">
         <v>93</v>
       </c>
-      <c r="AI3" s="305"/>
-      <c r="AJ3" s="305"/>
-      <c r="AK3" s="305"/>
-      <c r="AL3" s="305" t="s">
+      <c r="AI3" s="335"/>
+      <c r="AJ3" s="335"/>
+      <c r="AK3" s="335"/>
+      <c r="AL3" s="335" t="s">
         <v>94</v>
       </c>
-      <c r="AM3" s="305"/>
-      <c r="AN3" s="305"/>
-      <c r="AO3" s="305"/>
-      <c r="AP3" s="305"/>
-      <c r="AQ3" s="305"/>
-      <c r="AR3" s="391" t="s">
+      <c r="AM3" s="335"/>
+      <c r="AN3" s="335"/>
+      <c r="AO3" s="335"/>
+      <c r="AP3" s="335"/>
+      <c r="AQ3" s="335"/>
+      <c r="AR3" s="384" t="s">
         <v>95</v>
       </c>
-      <c r="AS3" s="391"/>
-      <c r="AT3" s="391" t="s">
+      <c r="AS3" s="384"/>
+      <c r="AT3" s="384" t="s">
         <v>96</v>
       </c>
-      <c r="AU3" s="391"/>
-      <c r="AV3" s="391"/>
-      <c r="AW3" s="407"/>
-    </row>
-    <row r="4" spans="1:51" ht="13">
+      <c r="AU3" s="384"/>
+      <c r="AV3" s="384"/>
+      <c r="AW3" s="399"/>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="I4" s="112" t="s">
         <v>97</v>
       </c>
-      <c r="J4" s="282" t="s">
+      <c r="J4" s="298" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="284"/>
-      <c r="L4" s="284" t="s">
+      <c r="K4" s="296"/>
+      <c r="L4" s="296" t="s">
         <v>148</v>
       </c>
-      <c r="M4" s="284"/>
-      <c r="N4" s="345" t="s">
+      <c r="M4" s="296"/>
+      <c r="N4" s="300" t="s">
         <v>100</v>
       </c>
-      <c r="O4" s="345"/>
-      <c r="P4" s="284" t="s">
+      <c r="O4" s="300"/>
+      <c r="P4" s="296" t="s">
         <v>101</v>
       </c>
-      <c r="Q4" s="284"/>
-      <c r="R4" s="284" t="s">
+      <c r="Q4" s="296"/>
+      <c r="R4" s="296" t="s">
         <v>102</v>
       </c>
-      <c r="S4" s="284"/>
-      <c r="T4" s="284" t="s">
+      <c r="S4" s="296"/>
+      <c r="T4" s="296" t="s">
         <v>103</v>
       </c>
-      <c r="U4" s="284"/>
-      <c r="V4" s="348" t="s">
+      <c r="U4" s="296"/>
+      <c r="V4" s="305" t="s">
         <v>104</v>
       </c>
-      <c r="W4" s="348"/>
-      <c r="X4" s="348" t="s">
+      <c r="W4" s="305"/>
+      <c r="X4" s="305" t="s">
         <v>105</v>
       </c>
-      <c r="Y4" s="348"/>
-      <c r="Z4" s="348" t="s">
+      <c r="Y4" s="305"/>
+      <c r="Z4" s="305" t="s">
         <v>106</v>
       </c>
-      <c r="AA4" s="348"/>
-      <c r="AB4" s="284" t="s">
+      <c r="AA4" s="305"/>
+      <c r="AB4" s="296" t="s">
         <v>107</v>
       </c>
-      <c r="AC4" s="284"/>
-      <c r="AD4" s="284" t="s">
+      <c r="AC4" s="296"/>
+      <c r="AD4" s="296" t="s">
         <v>108</v>
       </c>
-      <c r="AE4" s="284"/>
-      <c r="AF4" s="348" t="s">
+      <c r="AE4" s="296"/>
+      <c r="AF4" s="305" t="s">
         <v>109</v>
       </c>
-      <c r="AG4" s="348"/>
-      <c r="AH4" s="284" t="s">
+      <c r="AG4" s="305"/>
+      <c r="AH4" s="296" t="s">
         <v>110</v>
       </c>
-      <c r="AI4" s="284"/>
-      <c r="AJ4" s="284" t="s">
+      <c r="AI4" s="296"/>
+      <c r="AJ4" s="296" t="s">
         <v>111</v>
       </c>
-      <c r="AK4" s="284"/>
-      <c r="AL4" s="284" t="s">
+      <c r="AK4" s="296"/>
+      <c r="AL4" s="296" t="s">
         <v>112</v>
       </c>
-      <c r="AM4" s="284"/>
-      <c r="AN4" s="284" t="s">
+      <c r="AM4" s="296"/>
+      <c r="AN4" s="296" t="s">
         <v>113</v>
       </c>
-      <c r="AO4" s="284"/>
-      <c r="AP4" s="284" t="s">
+      <c r="AO4" s="296"/>
+      <c r="AP4" s="296" t="s">
         <v>114</v>
       </c>
-      <c r="AQ4" s="284"/>
-      <c r="AR4" s="404" t="s">
+      <c r="AQ4" s="296"/>
+      <c r="AR4" s="400" t="s">
         <v>115</v>
       </c>
-      <c r="AS4" s="404"/>
-      <c r="AT4" s="404" t="s">
+      <c r="AS4" s="400"/>
+      <c r="AT4" s="400" t="s">
         <v>116</v>
       </c>
-      <c r="AU4" s="404"/>
-      <c r="AV4" s="404" t="s">
+      <c r="AU4" s="400"/>
+      <c r="AV4" s="400" t="s">
         <v>117</v>
       </c>
-      <c r="AW4" s="405"/>
-    </row>
-    <row r="5" spans="1:51" ht="13.5" thickBot="1">
+      <c r="AW4" s="401"/>
+    </row>
+    <row r="5" spans="1:51" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I5" s="113" t="s">
         <v>123</v>
       </c>
-      <c r="J5" s="409" t="s">
+      <c r="J5" s="404" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="401"/>
-      <c r="L5" s="401" t="s">
+      <c r="K5" s="402"/>
+      <c r="L5" s="402" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="401"/>
-      <c r="N5" s="410" t="s">
+      <c r="M5" s="402"/>
+      <c r="N5" s="405" t="s">
         <v>51</v>
       </c>
-      <c r="O5" s="410"/>
-      <c r="P5" s="401" t="s">
+      <c r="O5" s="405"/>
+      <c r="P5" s="402" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="401"/>
-      <c r="R5" s="401" t="s">
+      <c r="Q5" s="402"/>
+      <c r="R5" s="402" t="s">
         <v>49</v>
       </c>
-      <c r="S5" s="401"/>
-      <c r="T5" s="401" t="s">
+      <c r="S5" s="402"/>
+      <c r="T5" s="402" t="s">
         <v>47</v>
       </c>
-      <c r="U5" s="401"/>
+      <c r="U5" s="402"/>
       <c r="V5" s="403" t="s">
         <v>50</v>
       </c>
@@ -17969,52 +17980,52 @@
         <v>53</v>
       </c>
       <c r="AA5" s="403"/>
-      <c r="AB5" s="401" t="s">
+      <c r="AB5" s="402" t="s">
         <v>124</v>
       </c>
-      <c r="AC5" s="401"/>
-      <c r="AD5" s="401" t="s">
+      <c r="AC5" s="402"/>
+      <c r="AD5" s="402" t="s">
         <v>55</v>
       </c>
-      <c r="AE5" s="401"/>
+      <c r="AE5" s="402"/>
       <c r="AF5" s="403" t="s">
         <v>64</v>
       </c>
       <c r="AG5" s="403"/>
-      <c r="AH5" s="401" t="s">
+      <c r="AH5" s="402" t="s">
         <v>56</v>
       </c>
-      <c r="AI5" s="401"/>
-      <c r="AJ5" s="401" t="s">
+      <c r="AI5" s="402"/>
+      <c r="AJ5" s="402" t="s">
         <v>57</v>
       </c>
-      <c r="AK5" s="401"/>
-      <c r="AL5" s="401" t="s">
+      <c r="AK5" s="402"/>
+      <c r="AL5" s="402" t="s">
         <v>58</v>
       </c>
-      <c r="AM5" s="401"/>
-      <c r="AN5" s="401" t="s">
+      <c r="AM5" s="402"/>
+      <c r="AN5" s="402" t="s">
         <v>59</v>
       </c>
-      <c r="AO5" s="401"/>
-      <c r="AP5" s="401" t="s">
+      <c r="AO5" s="402"/>
+      <c r="AP5" s="402" t="s">
         <v>60</v>
       </c>
-      <c r="AQ5" s="401"/>
-      <c r="AR5" s="401" t="s">
+      <c r="AQ5" s="402"/>
+      <c r="AR5" s="402" t="s">
         <v>61</v>
       </c>
-      <c r="AS5" s="401"/>
-      <c r="AT5" s="401" t="s">
+      <c r="AS5" s="402"/>
+      <c r="AT5" s="402" t="s">
         <v>62</v>
       </c>
-      <c r="AU5" s="401"/>
-      <c r="AV5" s="401" t="s">
+      <c r="AU5" s="402"/>
+      <c r="AV5" s="402" t="s">
         <v>63</v>
       </c>
-      <c r="AW5" s="402"/>
-    </row>
-    <row r="6" spans="1:51" ht="36">
+      <c r="AW5" s="406"/>
+    </row>
+    <row r="6" spans="1:51" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A6" s="98" t="s">
         <v>118</v>
       </c>
@@ -18081,7 +18092,7 @@
       <c r="AV6" s="116"/>
       <c r="AW6" s="117"/>
     </row>
-    <row r="7" spans="1:51" ht="14.5">
+    <row r="7" spans="1:51" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="56">
         <v>1</v>
       </c>
@@ -18107,90 +18118,90 @@
         <v>183</v>
       </c>
       <c r="I7" s="122"/>
-      <c r="J7" s="399">
-        <v>1</v>
-      </c>
-      <c r="K7" s="400"/>
-      <c r="L7" s="399">
-        <v>1</v>
-      </c>
-      <c r="M7" s="400"/>
-      <c r="N7" s="399">
-        <v>1</v>
-      </c>
-      <c r="O7" s="400"/>
-      <c r="P7" s="399">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="400"/>
-      <c r="R7" s="399">
-        <v>1</v>
-      </c>
-      <c r="S7" s="400"/>
-      <c r="T7" s="399">
-        <v>1</v>
-      </c>
-      <c r="U7" s="400"/>
-      <c r="V7" s="399">
-        <v>1</v>
-      </c>
-      <c r="W7" s="400"/>
-      <c r="X7" s="399">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="400"/>
-      <c r="Z7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="400"/>
-      <c r="AB7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="400"/>
-      <c r="AD7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="400"/>
-      <c r="AF7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AG7" s="400"/>
-      <c r="AH7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="400"/>
-      <c r="AJ7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AK7" s="400"/>
-      <c r="AL7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AM7" s="400"/>
-      <c r="AN7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="400"/>
-      <c r="AP7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AQ7" s="400"/>
-      <c r="AR7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AS7" s="400"/>
-      <c r="AT7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AU7" s="400"/>
-      <c r="AV7" s="399">
-        <v>1</v>
-      </c>
-      <c r="AW7" s="400"/>
-      <c r="AX7" s="397"/>
-      <c r="AY7" s="398"/>
-    </row>
-    <row r="8" spans="1:51" ht="18" customHeight="1">
+      <c r="J7" s="395">
+        <v>1</v>
+      </c>
+      <c r="K7" s="396"/>
+      <c r="L7" s="395">
+        <v>1</v>
+      </c>
+      <c r="M7" s="396"/>
+      <c r="N7" s="395">
+        <v>1</v>
+      </c>
+      <c r="O7" s="396"/>
+      <c r="P7" s="395">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="396"/>
+      <c r="R7" s="395">
+        <v>1</v>
+      </c>
+      <c r="S7" s="396"/>
+      <c r="T7" s="395">
+        <v>1</v>
+      </c>
+      <c r="U7" s="396"/>
+      <c r="V7" s="395">
+        <v>1</v>
+      </c>
+      <c r="W7" s="396"/>
+      <c r="X7" s="395">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="396"/>
+      <c r="Z7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="396"/>
+      <c r="AB7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="396"/>
+      <c r="AD7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="396"/>
+      <c r="AF7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="396"/>
+      <c r="AH7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="396"/>
+      <c r="AJ7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="396"/>
+      <c r="AL7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="396"/>
+      <c r="AN7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="396"/>
+      <c r="AP7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="396"/>
+      <c r="AR7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="396"/>
+      <c r="AT7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AU7" s="396"/>
+      <c r="AV7" s="395">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="396"/>
+      <c r="AX7" s="407"/>
+      <c r="AY7" s="408"/>
+    </row>
+    <row r="8" spans="1:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56">
         <v>2</v>
       </c>
@@ -18216,90 +18227,90 @@
         <v>183</v>
       </c>
       <c r="I8" s="122"/>
-      <c r="J8" s="399">
-        <v>1</v>
-      </c>
-      <c r="K8" s="400"/>
-      <c r="L8" s="399">
-        <v>1</v>
-      </c>
-      <c r="M8" s="400"/>
-      <c r="N8" s="399">
-        <v>1</v>
-      </c>
-      <c r="O8" s="400"/>
-      <c r="P8" s="399">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="400"/>
-      <c r="R8" s="399">
-        <v>1</v>
-      </c>
-      <c r="S8" s="400"/>
-      <c r="T8" s="399">
-        <v>1</v>
-      </c>
-      <c r="U8" s="400"/>
-      <c r="V8" s="399">
-        <v>1</v>
-      </c>
-      <c r="W8" s="400"/>
-      <c r="X8" s="399">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="400"/>
-      <c r="Z8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="400"/>
-      <c r="AB8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="400"/>
-      <c r="AD8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="400"/>
-      <c r="AF8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="400"/>
-      <c r="AH8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="400"/>
-      <c r="AJ8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AK8" s="400"/>
-      <c r="AL8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AM8" s="400"/>
-      <c r="AN8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AO8" s="400"/>
-      <c r="AP8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AQ8" s="400"/>
-      <c r="AR8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AS8" s="400"/>
-      <c r="AT8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AU8" s="400"/>
-      <c r="AV8" s="399">
-        <v>1</v>
-      </c>
-      <c r="AW8" s="400"/>
-      <c r="AX8" s="397"/>
-      <c r="AY8" s="398"/>
-    </row>
-    <row r="9" spans="1:51" ht="18" customHeight="1">
+      <c r="J8" s="395">
+        <v>1</v>
+      </c>
+      <c r="K8" s="396"/>
+      <c r="L8" s="395">
+        <v>1</v>
+      </c>
+      <c r="M8" s="396"/>
+      <c r="N8" s="395">
+        <v>1</v>
+      </c>
+      <c r="O8" s="396"/>
+      <c r="P8" s="395">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="396"/>
+      <c r="R8" s="395">
+        <v>1</v>
+      </c>
+      <c r="S8" s="396"/>
+      <c r="T8" s="395">
+        <v>1</v>
+      </c>
+      <c r="U8" s="396"/>
+      <c r="V8" s="395">
+        <v>1</v>
+      </c>
+      <c r="W8" s="396"/>
+      <c r="X8" s="395">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="396"/>
+      <c r="Z8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="396"/>
+      <c r="AB8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="396"/>
+      <c r="AD8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="396"/>
+      <c r="AF8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="396"/>
+      <c r="AH8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="396"/>
+      <c r="AJ8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="396"/>
+      <c r="AL8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="396"/>
+      <c r="AN8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="396"/>
+      <c r="AP8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="396"/>
+      <c r="AR8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="396"/>
+      <c r="AT8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AU8" s="396"/>
+      <c r="AV8" s="395">
+        <v>1</v>
+      </c>
+      <c r="AW8" s="396"/>
+      <c r="AX8" s="407"/>
+      <c r="AY8" s="408"/>
+    </row>
+    <row r="9" spans="1:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56">
         <v>3</v>
       </c>
@@ -18325,88 +18336,88 @@
         <v>183</v>
       </c>
       <c r="I9" s="122"/>
-      <c r="J9" s="399">
-        <v>1</v>
-      </c>
-      <c r="K9" s="400"/>
-      <c r="L9" s="399">
-        <v>1</v>
-      </c>
-      <c r="M9" s="400"/>
-      <c r="N9" s="399">
-        <v>1</v>
-      </c>
-      <c r="O9" s="400"/>
-      <c r="P9" s="399">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="400"/>
-      <c r="R9" s="399">
-        <v>1</v>
-      </c>
-      <c r="S9" s="400"/>
-      <c r="T9" s="399">
-        <v>1</v>
-      </c>
-      <c r="U9" s="400"/>
-      <c r="V9" s="399">
-        <v>1</v>
-      </c>
-      <c r="W9" s="400"/>
-      <c r="X9" s="399">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="400"/>
-      <c r="Z9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="400"/>
-      <c r="AB9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="400"/>
-      <c r="AD9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="400"/>
-      <c r="AF9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="400"/>
-      <c r="AH9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="400"/>
-      <c r="AJ9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AK9" s="400"/>
-      <c r="AL9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AM9" s="400"/>
-      <c r="AN9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AO9" s="400"/>
-      <c r="AP9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AQ9" s="400"/>
-      <c r="AR9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AS9" s="400"/>
-      <c r="AT9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AU9" s="400"/>
-      <c r="AV9" s="399">
-        <v>1</v>
-      </c>
-      <c r="AW9" s="400"/>
-    </row>
-    <row r="10" spans="1:51" ht="14.5">
+      <c r="J9" s="395">
+        <v>1</v>
+      </c>
+      <c r="K9" s="396"/>
+      <c r="L9" s="395">
+        <v>1</v>
+      </c>
+      <c r="M9" s="396"/>
+      <c r="N9" s="395">
+        <v>1</v>
+      </c>
+      <c r="O9" s="396"/>
+      <c r="P9" s="395">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="396"/>
+      <c r="R9" s="395">
+        <v>1</v>
+      </c>
+      <c r="S9" s="396"/>
+      <c r="T9" s="395">
+        <v>1</v>
+      </c>
+      <c r="U9" s="396"/>
+      <c r="V9" s="395">
+        <v>1</v>
+      </c>
+      <c r="W9" s="396"/>
+      <c r="X9" s="395">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="396"/>
+      <c r="Z9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="396"/>
+      <c r="AB9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="396"/>
+      <c r="AD9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="396"/>
+      <c r="AF9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="396"/>
+      <c r="AH9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="396"/>
+      <c r="AJ9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="396"/>
+      <c r="AL9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="396"/>
+      <c r="AN9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="396"/>
+      <c r="AP9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="396"/>
+      <c r="AR9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="396"/>
+      <c r="AT9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AU9" s="396"/>
+      <c r="AV9" s="395">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="396"/>
+    </row>
+    <row r="10" spans="1:51" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="56">
         <v>4</v>
       </c>
@@ -18432,48 +18443,48 @@
         <v>183</v>
       </c>
       <c r="I10" s="123"/>
-      <c r="J10" s="399"/>
-      <c r="K10" s="400"/>
-      <c r="L10" s="399"/>
-      <c r="M10" s="400"/>
-      <c r="N10" s="399"/>
-      <c r="O10" s="400"/>
-      <c r="P10" s="399"/>
-      <c r="Q10" s="400"/>
-      <c r="R10" s="399"/>
-      <c r="S10" s="400"/>
-      <c r="T10" s="399"/>
-      <c r="U10" s="400"/>
-      <c r="V10" s="399"/>
-      <c r="W10" s="400"/>
-      <c r="X10" s="399"/>
-      <c r="Y10" s="400"/>
-      <c r="Z10" s="399"/>
-      <c r="AA10" s="400"/>
-      <c r="AB10" s="399"/>
-      <c r="AC10" s="400"/>
-      <c r="AD10" s="399"/>
-      <c r="AE10" s="400"/>
-      <c r="AF10" s="399"/>
-      <c r="AG10" s="400"/>
-      <c r="AH10" s="399"/>
-      <c r="AI10" s="400"/>
-      <c r="AJ10" s="399"/>
-      <c r="AK10" s="400"/>
-      <c r="AL10" s="399"/>
-      <c r="AM10" s="400"/>
-      <c r="AN10" s="399"/>
-      <c r="AO10" s="400"/>
-      <c r="AP10" s="399"/>
-      <c r="AQ10" s="400"/>
-      <c r="AR10" s="399"/>
-      <c r="AS10" s="400"/>
-      <c r="AT10" s="399"/>
-      <c r="AU10" s="400"/>
-      <c r="AV10" s="399"/>
-      <c r="AW10" s="400"/>
-    </row>
-    <row r="11" spans="1:51" ht="13">
+      <c r="J10" s="395"/>
+      <c r="K10" s="396"/>
+      <c r="L10" s="395"/>
+      <c r="M10" s="396"/>
+      <c r="N10" s="395"/>
+      <c r="O10" s="396"/>
+      <c r="P10" s="395"/>
+      <c r="Q10" s="396"/>
+      <c r="R10" s="395"/>
+      <c r="S10" s="396"/>
+      <c r="T10" s="395"/>
+      <c r="U10" s="396"/>
+      <c r="V10" s="395"/>
+      <c r="W10" s="396"/>
+      <c r="X10" s="395"/>
+      <c r="Y10" s="396"/>
+      <c r="Z10" s="395"/>
+      <c r="AA10" s="396"/>
+      <c r="AB10" s="395"/>
+      <c r="AC10" s="396"/>
+      <c r="AD10" s="395"/>
+      <c r="AE10" s="396"/>
+      <c r="AF10" s="395"/>
+      <c r="AG10" s="396"/>
+      <c r="AH10" s="395"/>
+      <c r="AI10" s="396"/>
+      <c r="AJ10" s="395"/>
+      <c r="AK10" s="396"/>
+      <c r="AL10" s="395"/>
+      <c r="AM10" s="396"/>
+      <c r="AN10" s="395"/>
+      <c r="AO10" s="396"/>
+      <c r="AP10" s="395"/>
+      <c r="AQ10" s="396"/>
+      <c r="AR10" s="395"/>
+      <c r="AS10" s="396"/>
+      <c r="AT10" s="395"/>
+      <c r="AU10" s="396"/>
+      <c r="AV10" s="395"/>
+      <c r="AW10" s="396"/>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="I11" s="124" t="s">
         <v>190</v>
       </c>
@@ -18597,7 +18608,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="12" spans="1:51" s="127" customFormat="1" ht="13">
+    <row r="12" spans="1:51" s="127" customFormat="1" x14ac:dyDescent="0.25">
       <c r="I12" s="128"/>
       <c r="J12" s="245">
         <v>18</v>
@@ -18684,7 +18695,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="13" spans="1:51" ht="14">
+    <row r="13" spans="1:51" ht="15" x14ac:dyDescent="0.25">
       <c r="I13" s="129" t="s">
         <v>193</v>
       </c>
@@ -18773,7 +18784,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="14" spans="1:51">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="I14" s="130" t="s">
         <v>194</v>
       </c>
@@ -18862,7 +18873,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="15" spans="1:51" ht="13">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="I15" s="129" t="s">
         <v>195</v>
       </c>
@@ -18951,7 +18962,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:51" ht="13">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="I16" s="130" t="s">
         <v>196</v>
       </c>
@@ -19040,7 +19051,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="17" spans="9:50" ht="13">
+    <row r="17" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I17" s="129" t="s">
         <v>197</v>
       </c>
@@ -19129,7 +19140,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="9:50" ht="13">
+    <row r="18" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I18" s="130" t="s">
         <v>198</v>
       </c>
@@ -19218,7 +19229,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="19" spans="9:50">
+    <row r="19" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I19" s="129" t="s">
         <v>199</v>
       </c>
@@ -19307,7 +19318,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="9:50" ht="14">
+    <row r="20" spans="9:50" ht="15" x14ac:dyDescent="0.25">
       <c r="I20" s="130" t="s">
         <v>200</v>
       </c>
@@ -19396,7 +19407,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="21" spans="9:50">
+    <row r="21" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I21" s="129" t="s">
         <v>201</v>
       </c>
@@ -19485,7 +19496,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="9:50">
+    <row r="22" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I22" s="130" t="s">
         <v>202</v>
       </c>
@@ -19574,7 +19585,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="23" spans="9:50">
+    <row r="23" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I23" s="129" t="s">
         <v>203</v>
       </c>
@@ -19663,7 +19674,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="24" spans="9:50" ht="13" thickBot="1">
+    <row r="24" spans="9:50" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I24" s="130" t="s">
         <v>204</v>
       </c>
@@ -19752,7 +19763,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="25" spans="9:50" ht="16.5" thickBot="1">
+    <row r="25" spans="9:50" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J25" s="254"/>
       <c r="K25" s="255"/>
       <c r="L25" s="255"/>
@@ -19782,7 +19793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="9:50" s="127" customFormat="1" ht="13">
+    <row r="26" spans="9:50" s="127" customFormat="1" x14ac:dyDescent="0.25">
       <c r="I26" s="131" t="s">
         <v>205</v>
       </c>
@@ -19871,7 +19882,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="9:50" ht="13">
+    <row r="27" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I27" s="129" t="s">
         <v>193</v>
       </c>
@@ -19960,7 +19971,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="9:50" ht="14">
+    <row r="28" spans="9:50" ht="15" x14ac:dyDescent="0.25">
       <c r="I28" s="130" t="s">
         <v>194</v>
       </c>
@@ -20049,7 +20060,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="9:50" ht="13">
+    <row r="29" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I29" s="129" t="s">
         <v>195</v>
       </c>
@@ -20138,7 +20149,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="9:50" ht="13">
+    <row r="30" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I30" s="130" t="s">
         <v>196</v>
       </c>
@@ -20227,7 +20238,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="9:50" ht="13">
+    <row r="31" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I31" s="129" t="s">
         <v>197</v>
       </c>
@@ -20316,7 +20327,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="9:50" s="134" customFormat="1" ht="13">
+    <row r="32" spans="9:50" s="134" customFormat="1" x14ac:dyDescent="0.25">
       <c r="I32" s="133" t="s">
         <v>198</v>
       </c>
@@ -20405,7 +20416,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="9:50" s="134" customFormat="1" ht="13">
+    <row r="33" spans="9:50" s="134" customFormat="1" x14ac:dyDescent="0.25">
       <c r="I33" s="132" t="s">
         <v>199</v>
       </c>
@@ -20494,7 +20505,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="9:50" s="134" customFormat="1" ht="14">
+    <row r="34" spans="9:50" s="134" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="I34" s="133" t="s">
         <v>200</v>
       </c>
@@ -20583,7 +20594,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="9:50" s="134" customFormat="1" ht="13">
+    <row r="35" spans="9:50" s="134" customFormat="1" x14ac:dyDescent="0.25">
       <c r="I35" s="132" t="s">
         <v>201</v>
       </c>
@@ -20671,7 +20682,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="9:50" s="134" customFormat="1" ht="13">
+    <row r="36" spans="9:50" s="134" customFormat="1" x14ac:dyDescent="0.25">
       <c r="I36" s="133" t="s">
         <v>202</v>
       </c>
@@ -20760,7 +20771,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="9:50" s="134" customFormat="1" ht="13">
+    <row r="37" spans="9:50" s="134" customFormat="1" x14ac:dyDescent="0.25">
       <c r="I37" s="132" t="s">
         <v>203</v>
       </c>
@@ -20849,7 +20860,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="9:50" s="134" customFormat="1" ht="13">
+    <row r="38" spans="9:50" s="134" customFormat="1" x14ac:dyDescent="0.25">
       <c r="I38" s="133" t="s">
         <v>204</v>
       </c>
@@ -20938,7 +20949,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="9:50" ht="16">
+    <row r="39" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="J39" s="135"/>
       <c r="K39" s="135"/>
       <c r="L39" s="135"/>
@@ -20965,7 +20976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="9:50" s="127" customFormat="1" ht="13.5" customHeight="1">
+    <row r="40" spans="9:50" s="127" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I40" s="136" t="s">
         <v>206</v>
       </c>
@@ -21054,7 +21065,7 @@
         <v>6153</v>
       </c>
     </row>
-    <row r="41" spans="9:50" ht="16">
+    <row r="41" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="I41" s="129" t="s">
         <v>193</v>
       </c>
@@ -21143,7 +21154,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="42" spans="9:50" ht="16">
+    <row r="42" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="I42" s="129" t="s">
         <v>194</v>
       </c>
@@ -21232,7 +21243,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="43" spans="9:50" ht="16">
+    <row r="43" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="I43" s="129" t="s">
         <v>195</v>
       </c>
@@ -21321,7 +21332,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="44" spans="9:50" ht="16">
+    <row r="44" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="I44" s="129" t="s">
         <v>196</v>
       </c>
@@ -21410,7 +21421,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="45" spans="9:50" ht="16">
+    <row r="45" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="I45" s="129" t="s">
         <v>197</v>
       </c>
@@ -21499,7 +21510,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="46" spans="9:50" ht="16">
+    <row r="46" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="I46" s="130" t="s">
         <v>198</v>
       </c>
@@ -21588,7 +21599,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="47" spans="9:50" ht="16">
+    <row r="47" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="I47" s="129" t="s">
         <v>199</v>
       </c>
@@ -21677,7 +21688,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="48" spans="9:50" ht="14">
+    <row r="48" spans="9:50" ht="15" x14ac:dyDescent="0.25">
       <c r="I48" s="129" t="s">
         <v>200</v>
       </c>
@@ -21766,7 +21777,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="49" spans="9:50">
+    <row r="49" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I49" s="129" t="s">
         <v>201</v>
       </c>
@@ -21855,7 +21866,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="50" spans="9:50">
+    <row r="50" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I50" s="129" t="s">
         <v>202</v>
       </c>
@@ -21944,7 +21955,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="51" spans="9:50">
+    <row r="51" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I51" s="129" t="s">
         <v>203</v>
       </c>
@@ -22033,7 +22044,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="52" spans="9:50">
+    <row r="52" spans="9:50" x14ac:dyDescent="0.25">
       <c r="I52" s="130" t="s">
         <v>204</v>
       </c>
@@ -22122,7 +22133,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="53" spans="9:50" ht="16">
+    <row r="53" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="J53" s="137"/>
       <c r="K53" s="137"/>
       <c r="L53" s="137"/>
@@ -22145,7 +22156,7 @@
       <c r="AC53" s="137"/>
       <c r="AD53" s="135"/>
     </row>
-    <row r="55" spans="9:50" ht="16">
+    <row r="55" spans="9:50" ht="14.25" x14ac:dyDescent="0.25">
       <c r="J55" s="135"/>
       <c r="K55" s="135"/>
       <c r="L55" s="135"/>
@@ -22169,6 +22180,116 @@
     </row>
   </sheetData>
   <mergeCells count="134">
+    <mergeCell ref="AX8:AY8"/>
+    <mergeCell ref="AX7:AY7"/>
+    <mergeCell ref="AV8:AW8"/>
+    <mergeCell ref="AV10:AW10"/>
+    <mergeCell ref="AR10:AS10"/>
+    <mergeCell ref="AT10:AU10"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="AT5:AU5"/>
+    <mergeCell ref="AV5:AW5"/>
+    <mergeCell ref="AH5:AI5"/>
+    <mergeCell ref="AJ5:AK5"/>
+    <mergeCell ref="AL5:AM5"/>
+    <mergeCell ref="AN5:AO5"/>
+    <mergeCell ref="AP5:AQ5"/>
+    <mergeCell ref="AR5:AS5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AH2:AQ2"/>
+    <mergeCell ref="AR2:AW2"/>
+    <mergeCell ref="J3:O3"/>
+    <mergeCell ref="P3:U3"/>
+    <mergeCell ref="V3:AA3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="AL3:AQ3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="AT3:AW3"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="AF9:AG9"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="J2:U2"/>
+    <mergeCell ref="V2:AG2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="AF5:AG5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="AL10:AM10"/>
+    <mergeCell ref="AN10:AO10"/>
+    <mergeCell ref="AP10:AQ10"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="AJ10:AK10"/>
+    <mergeCell ref="AH10:AI10"/>
+    <mergeCell ref="AJ8:AK8"/>
+    <mergeCell ref="AB9:AC9"/>
+    <mergeCell ref="AH9:AI9"/>
+    <mergeCell ref="AD9:AE9"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AB8:AC8"/>
+    <mergeCell ref="AD8:AE8"/>
+    <mergeCell ref="AF8:AG8"/>
+    <mergeCell ref="AH8:AI8"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AB10:AC10"/>
+    <mergeCell ref="AD10:AE10"/>
+    <mergeCell ref="AF10:AG10"/>
+    <mergeCell ref="AJ9:AK9"/>
+    <mergeCell ref="AJ7:AK7"/>
+    <mergeCell ref="AV7:AW7"/>
+    <mergeCell ref="AT9:AU9"/>
+    <mergeCell ref="AV9:AW9"/>
+    <mergeCell ref="AR7:AS7"/>
+    <mergeCell ref="AT7:AU7"/>
+    <mergeCell ref="AR8:AS8"/>
+    <mergeCell ref="AT8:AU8"/>
+    <mergeCell ref="AN8:AO8"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AN7:AO7"/>
+    <mergeCell ref="AP7:AQ7"/>
+    <mergeCell ref="AL9:AM9"/>
+    <mergeCell ref="AN9:AO9"/>
+    <mergeCell ref="AP9:AQ9"/>
+    <mergeCell ref="AR9:AS9"/>
+    <mergeCell ref="AP8:AQ8"/>
+    <mergeCell ref="AL8:AM8"/>
     <mergeCell ref="X7:Y7"/>
     <mergeCell ref="Z7:AA7"/>
     <mergeCell ref="T7:U7"/>
@@ -22193,116 +22314,6 @@
     <mergeCell ref="X10:Y10"/>
     <mergeCell ref="P8:Q8"/>
     <mergeCell ref="L8:M8"/>
-    <mergeCell ref="AJ7:AK7"/>
-    <mergeCell ref="AV7:AW7"/>
-    <mergeCell ref="AT9:AU9"/>
-    <mergeCell ref="AV9:AW9"/>
-    <mergeCell ref="AR7:AS7"/>
-    <mergeCell ref="AT7:AU7"/>
-    <mergeCell ref="AR8:AS8"/>
-    <mergeCell ref="AT8:AU8"/>
-    <mergeCell ref="AN8:AO8"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AN7:AO7"/>
-    <mergeCell ref="AP7:AQ7"/>
-    <mergeCell ref="AL9:AM9"/>
-    <mergeCell ref="AN9:AO9"/>
-    <mergeCell ref="AP9:AQ9"/>
-    <mergeCell ref="AR9:AS9"/>
-    <mergeCell ref="AP8:AQ8"/>
-    <mergeCell ref="AL8:AM8"/>
-    <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="AB8:AC8"/>
-    <mergeCell ref="AD8:AE8"/>
-    <mergeCell ref="AF8:AG8"/>
-    <mergeCell ref="AH8:AI8"/>
-    <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="AB10:AC10"/>
-    <mergeCell ref="AD10:AE10"/>
-    <mergeCell ref="AF10:AG10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="AJ10:AK10"/>
-    <mergeCell ref="AH10:AI10"/>
-    <mergeCell ref="AJ8:AK8"/>
-    <mergeCell ref="AB9:AC9"/>
-    <mergeCell ref="AH9:AI9"/>
-    <mergeCell ref="AD9:AE9"/>
-    <mergeCell ref="AJ9:AK9"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="AF9:AG9"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="AF7:AG7"/>
-    <mergeCell ref="J2:U2"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="AB5:AC5"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="AF5:AG5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="AH2:AQ2"/>
-    <mergeCell ref="AR2:AW2"/>
-    <mergeCell ref="J3:O3"/>
-    <mergeCell ref="P3:U3"/>
-    <mergeCell ref="V3:AA3"/>
-    <mergeCell ref="AB3:AG3"/>
-    <mergeCell ref="AH3:AK3"/>
-    <mergeCell ref="AL3:AQ3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="AT3:AW3"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AX8:AY8"/>
-    <mergeCell ref="AX7:AY7"/>
-    <mergeCell ref="AV8:AW8"/>
-    <mergeCell ref="AV10:AW10"/>
-    <mergeCell ref="AR10:AS10"/>
-    <mergeCell ref="AT10:AU10"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="AT5:AU5"/>
-    <mergeCell ref="AV5:AW5"/>
-    <mergeCell ref="AH5:AI5"/>
-    <mergeCell ref="AJ5:AK5"/>
-    <mergeCell ref="AL5:AM5"/>
-    <mergeCell ref="AN5:AO5"/>
-    <mergeCell ref="AP5:AQ5"/>
-    <mergeCell ref="AR5:AS5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="AL10:AM10"/>
-    <mergeCell ref="AN10:AO10"/>
-    <mergeCell ref="AP10:AQ10"/>
-    <mergeCell ref="R9:S9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22312,14 +22323,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B25131-1F3A-4E19-A2F4-9B15E35E2B1D}">
   <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="75" t="s">
         <v>243</v>
       </c>
@@ -22330,7 +22341,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="75" t="s">
         <v>25</v>
       </c>
@@ -22350,7 +22361,7 @@
       <c r="Q2" s="172"/>
       <c r="S2" s="172"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="75" t="s">
         <v>26</v>
       </c>
@@ -22362,7 +22373,7 @@
         <v>0.69134075642559678</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="75" t="s">
         <v>27</v>
       </c>
@@ -22373,7 +22384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="75" t="s">
         <v>28</v>
       </c>
@@ -22384,7 +22395,7 @@
         <v>0.99999234682325944</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="75" t="s">
         <v>29</v>
       </c>
@@ -22395,7 +22406,7 @@
         <v>0.54145583965164246</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="75" t="s">
         <v>30</v>
       </c>
@@ -22406,7 +22417,7 @@
         <v>0.90599397567358553</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="75" t="s">
         <v>31</v>
       </c>
@@ -22417,7 +22428,7 @@
         <v>0.73534809985241989</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="75" t="s">
         <v>32</v>
       </c>
@@ -22428,7 +22439,7 @@
         <v>0.99999066458348385</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="75" t="s">
         <v>33</v>
       </c>
@@ -22440,7 +22451,7 @@
         <v>0.69312395080019773</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="75" t="s">
         <v>34</v>
       </c>
@@ -22461,7 +22472,7 @@
       <c r="S11" s="172"/>
       <c r="U11" s="172"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="75" t="s">
         <v>35</v>
       </c>
@@ -22473,7 +22484,7 @@
         <v>0.99999193080047299</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="75" t="s">
         <v>36</v>
       </c>
@@ -22484,7 +22495,7 @@
         <v>0.96918060324206157</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="75" t="s">
         <v>37</v>
       </c>
@@ -22495,7 +22506,7 @@
         <v>0.99998455951593024</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="75" t="s">
         <v>38</v>
       </c>
@@ -22506,7 +22517,7 @@
         <v>0.88015812975737995</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="75" t="s">
         <v>39</v>
       </c>
@@ -22517,7 +22528,7 @@
         <v>0.99999452122042165</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="75" t="s">
         <v>40</v>
       </c>
@@ -22529,7 +22540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="75" t="s">
         <v>41</v>
       </c>
@@ -22541,7 +22552,7 @@
         <v>0.99999000136174898</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="75" t="s">
         <v>240</v>
       </c>
@@ -22552,7 +22563,7 @@
         <v>0.99975473154491334</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="75" t="s">
         <v>43</v>
       </c>
@@ -22563,7 +22574,7 @@
         <v>0.99999584660002983</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="75" t="s">
         <v>44</v>
       </c>
